--- a/AAII_Financials/Quarterly/SBRA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBRA_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>SBRA</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>163400</v>
+      </c>
+      <c r="E8" s="3">
         <v>161600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>161200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>161300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>165000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>140800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>156000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>163100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>135700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>128600</v>
-      </c>
-      <c r="M8" s="3">
-        <v>152400</v>
       </c>
       <c r="N8" s="3">
         <v>152400</v>
       </c>
       <c r="O8" s="3">
+        <v>152400</v>
+      </c>
+      <c r="P8" s="3">
         <v>151500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>142100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>153900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>149300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>155800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>149800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>152500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>136800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>139200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>151800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>166300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>166100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>166500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>111800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>64700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>62700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>61800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>61900</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>45200</v>
+      </c>
+      <c r="E9" s="3">
         <v>44500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>44000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>43600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>39200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>36700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>34000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>33100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>30900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>30000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>28500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>28000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>26900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>26500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>27000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>26000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>24000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>24200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>12500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>12600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>12300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>2400</v>
-      </c>
-      <c r="AE9" s="3">
-        <v>1400</v>
       </c>
       <c r="AF9" s="3">
         <v>1400</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>118200</v>
+      </c>
+      <c r="E10" s="3">
         <v>117100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>117200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>117700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>125800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>104100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>122000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>130000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>104800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>98600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>123900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>124400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>124600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>115600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>127600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>122300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>129800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>125800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>128300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>124800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>126700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>139200</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>154000</v>
       </c>
       <c r="Z10" s="3">
         <v>154000</v>
       </c>
       <c r="AA10" s="3">
+        <v>154000</v>
+      </c>
+      <c r="AB10" s="3">
         <v>160600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>106700</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>60300</v>
       </c>
       <c r="AD10" s="3">
         <v>60300</v>
       </c>
       <c r="AE10" s="3">
+        <v>60300</v>
+      </c>
+      <c r="AF10" s="3">
         <v>60400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,89 +1298,92 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>8600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>21200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>61000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>43400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2200</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>1700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>8300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>14600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-45100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>103100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2900</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>500</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>600</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
@@ -1374,46 +1393,49 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E15" s="3">
         <v>43200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>44100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>52800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>49900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>47400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>45200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>45300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>45100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>45000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>44500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>44400</v>
-      </c>
-      <c r="O15" s="3">
-        <v>44200</v>
       </c>
       <c r="P15" s="3">
         <v>44200</v>
@@ -1425,49 +1447,52 @@
         <v>44200</v>
       </c>
       <c r="S15" s="3">
+        <v>44200</v>
+      </c>
+      <c r="T15" s="3">
         <v>44000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>43100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>49500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>44900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>48100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>48500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>46800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>48000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>51600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>25900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>17200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>19100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>17200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>144300</v>
+      </c>
+      <c r="E17" s="3">
         <v>131300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>131200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>148100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>153900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>186800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>129700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>117200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>160300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>115200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>110900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>114700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>111800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>114000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>112000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>111500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>116500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>125300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>67000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>211100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>141700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>115500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>105500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>105900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>109500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>97500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>49000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>45800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>40800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E18" s="3">
         <v>30300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>30000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>13200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>11100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-46000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>26300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>45900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-24600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>41500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>37700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>39700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>28100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>41900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>37800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>39300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>24500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>85500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-74300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>36300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>60800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>60200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>57000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>14300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>15700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>16900</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>21000</v>
       </c>
       <c r="AF18" s="3">
         <v>21000</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,192 +1747,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-44900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-8500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-22000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-96000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-9200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-173500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-11900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-15700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>140600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>47400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>5000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>60500</v>
+      </c>
+      <c r="E21" s="3">
         <v>28600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>65700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>44100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-34900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-2100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>62200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>86100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>21300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>55400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-87600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>78500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>80600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>80500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>74300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>80400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>84900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>67200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>134000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-32100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>29900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>84400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>248200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>111000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>155400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>41400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>37900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>38100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>40600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1991,100 +2030,106 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-14600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>21500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-8800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-84800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-49500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>17100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>40900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-23800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>10300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-132100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>34100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>36500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>36300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>30100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>36300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>40900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>24100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>84500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-77100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-18200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>36000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>201400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>63000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>104500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>14900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>20700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>19000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>23400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2092,91 +2137,94 @@
         <v>500</v>
       </c>
       <c r="E24" s="3">
+        <v>500</v>
+      </c>
+      <c r="F24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>600</v>
-      </c>
-      <c r="I24" s="3">
-        <v>300</v>
       </c>
       <c r="J24" s="3">
         <v>300</v>
       </c>
       <c r="K24" s="3">
+        <v>300</v>
+      </c>
+      <c r="L24" s="3">
         <v>500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>600</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>500</v>
       </c>
       <c r="AA24" s="3">
         <v>500</v>
       </c>
       <c r="AB24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AC24" s="3">
         <v>-200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-15100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>21200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-84900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-50100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>16800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>40600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-24400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-132600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>33400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>37100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>36500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>29600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>35200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>39700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>23300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>83700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-77700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-19400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>35200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>200800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>62500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>104000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>15100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>20500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>18800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>23200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-15100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>21200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-84900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-50100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>16800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>40600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-24400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-132600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>33400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>37100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>36500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>29600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>35200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>39700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>23300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>83700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-77700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-19400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>35200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>193600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>59900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>101400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>12500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>18000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>16300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>20600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E32" s="3">
         <v>44900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>8500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>22000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>96000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>9200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>173500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>11900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>15700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-140600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-47400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-15100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>21200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-84900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-50100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>16800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>40600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-24400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-132600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>33400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>37100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>36500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>29600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>35200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>39700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>23300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>83700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-77700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-19400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>35200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>193600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>59900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>101400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>12500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>18000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>16300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>20600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-15100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>21200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-84900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-50100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>16800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>40600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-24400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-132600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>33400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>37100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>36500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>29600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>35200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>39700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>23300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>83700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-77700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-19400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>35200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>193600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>59900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>101400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>12500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>18000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>16300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>20600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E41" s="3">
         <v>33300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>27200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>49300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>26300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>67200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>24800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>112000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>546300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>69300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>59100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>35000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>28300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>54100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>39100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>29400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>47600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>22900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>50200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>36300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>38800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>46400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>518600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>30900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>13200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>12800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>25700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,8 +3625,11 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3628,8 +3720,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,8 +3815,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3794,26 +3892,29 @@
       <c r="Z45" s="3">
         <v>0</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>8</v>
+      <c r="AA45" s="3">
+        <v>0</v>
       </c>
       <c r="AB45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AC45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD45" s="3">
         <v>141200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>126000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>125300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>116400</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3904,272 +4005,281 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>557500</v>
+      </c>
+      <c r="E47" s="3">
         <v>553700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>557400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>548500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>546400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>597900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>615300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>491000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>495800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>215800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>219200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>385000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>391600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>397600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>379700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>400100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>426800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>432600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>439400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>444900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>453800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>454700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>456200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>455800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>114400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>149800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>94200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>96500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>96000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>94500</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4617300</v>
+      </c>
+      <c r="E48" s="3">
         <v>4603000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4751900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4797000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4959300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5018900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5045100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5156100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5162900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5228700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5269400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5279400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5285000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5306300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5358500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5363200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5350700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5354400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5388400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5447200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5853500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5975600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5993700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6108800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5994400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5972800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1995900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1993600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2009900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1999800</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>30900</v>
+      </c>
+      <c r="E49" s="3">
         <v>32700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>36000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>39400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>40100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>48300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>49800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>52900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>54100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>76400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>79700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>81500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>82800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>85900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>93500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>96800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>101500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>105000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>108900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>119700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>131100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>142900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>156300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>161400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>167100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>262800</v>
-      </c>
-      <c r="AC49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD49" s="3" t="s">
         <v>8</v>
@@ -4180,8 +4290,11 @@
       <c r="AF49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E52" s="3">
         <v>5600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4900</v>
-      </c>
-      <c r="I52" s="3">
-        <v>4400</v>
       </c>
       <c r="J52" s="3">
         <v>4400</v>
       </c>
       <c r="K52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="L52" s="3">
         <v>3900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>5100</v>
-      </c>
-      <c r="M52" s="3">
-        <v>4600</v>
       </c>
       <c r="N52" s="3">
         <v>4600</v>
       </c>
       <c r="O52" s="3">
+        <v>4600</v>
+      </c>
+      <c r="P52" s="3">
         <v>6400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>10000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>9900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>280500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>103200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>186800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>11800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>68800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>12500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>11200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5386200</v>
+      </c>
+      <c r="E54" s="3">
         <v>5380600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5524300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5556300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5747700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5844900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5961400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5884900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5966700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6209500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5822100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5963800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5985600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5991600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6023600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6092300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6069300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6068000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6123200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6455100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6665300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6910300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7028100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6984600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7032300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6588300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2254000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2240100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2265900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2239400</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,100 +4837,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>120500</v>
+      </c>
+      <c r="E57" s="3">
         <v>106900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>105500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>121600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>124100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>123200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>101100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>92900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>121500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>108600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>103300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>105900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>130200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>125600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>143300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>112500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>98400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>92100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>90800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>72900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>94800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>86900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>105300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>102400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>102500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>116100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>37100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>33400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>39600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4892,58 +5025,61 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16500</v>
+      </c>
+      <c r="E59" s="3">
         <v>21100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>22000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>25400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18100</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S59" s="3">
-        <v>9800</v>
+      <c r="S59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T59" s="3">
         <v>9800</v>
@@ -4952,16 +5088,16 @@
         <v>9800</v>
       </c>
       <c r="V59" s="3">
+        <v>9800</v>
+      </c>
+      <c r="W59" s="3">
         <v>10000</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
+      <c r="Y59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z59" s="3">
         <v>0</v>
@@ -4984,8 +5120,11 @@
       <c r="AF59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5076,100 +5215,106 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2414100</v>
+      </c>
+      <c r="E61" s="3">
         <v>2349500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2420000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2396600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2506800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2446900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2480200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2357500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2394500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2702100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2266300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2281600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2372400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2423000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2455300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2479300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2402100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2603100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2686000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3230200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3232000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3368600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3423800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3361100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3394500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3005500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1220100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1202400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1210700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1187400</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5260,8 +5405,11 @@
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2583600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2511700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2580600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2580100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2691300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2636200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2643700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2523400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2587200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2880400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2439100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2460400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2576400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2627300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2662300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2697100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2580800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2785600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2867100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3408700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3414900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3547400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3624600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3562400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3599500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3219200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1257300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1235800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1250300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1225600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5918,7 +6085,7 @@
         <v>0</v>
       </c>
       <c r="Z70" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA70" s="3">
         <v>100</v>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1718300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1665000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1579900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1531200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1451900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1296900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1177000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1124100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1095200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1001200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-944500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-746500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-716200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-689800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-663900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-631300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-573300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-523700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-460800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-462600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-271600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-171100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-125600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-238600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-217200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-225500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-214100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-203600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-192200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-185000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2802500</v>
+      </c>
+      <c r="E76" s="3">
         <v>2868900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2943700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2976200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3056400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3208700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3317700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3361500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3379500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3329100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3383100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3503400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3409200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3364300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3361300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3395200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3488500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3282400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3256100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3046500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3250400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3362900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3403500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3422100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3432700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3369000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>996600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1004300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1015500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1013800</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>17200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-15100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>21200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-84900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-50100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>16800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>40600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-24400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-132600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>33400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>37100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>36500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>29600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>35200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>39700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>23300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>83700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-77700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-19400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>35200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>193600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>59900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>101400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>12500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>18000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>16300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>20600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,46 +7002,47 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E83" s="3">
         <v>43200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>44100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>52800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>49900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>47400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>45200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>45300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>45100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>45000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>44500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>44400</v>
-      </c>
-      <c r="O83" s="3">
-        <v>44200</v>
       </c>
       <c r="P83" s="3">
         <v>44200</v>
@@ -6856,49 +7054,52 @@
         <v>44200</v>
       </c>
       <c r="S83" s="3">
+        <v>44200</v>
+      </c>
+      <c r="T83" s="3">
         <v>44000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>43100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>49500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>44900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>48100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>48500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>46800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>48000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>51000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>26600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>17200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>19100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>17200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E89" s="3">
         <v>83200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>70300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>68300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>67600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>108500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>76600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>63100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>97900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>106200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>83700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>68500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>89400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>96900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>93800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>74800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>95500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>85100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>137900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>54000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>77600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>71500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>109900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>101600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>82500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>22700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>31600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>42900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>39300</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,61 +7702,62 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-38900</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
       </c>
       <c r="F91" s="3">
+        <v>0</v>
+      </c>
+      <c r="G91" s="3">
         <v>-39600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-63400</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
+        <v>0</v>
+      </c>
+      <c r="K91" s="3">
         <v>-20600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-37300</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-33500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-28700</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-25700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-67300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-36200</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>8</v>
@@ -7545,38 +7765,41 @@
       <c r="V91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W91" s="3">
+      <c r="W91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X91" s="3">
         <v>-22500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-25000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AF91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-61800</v>
+      </c>
+      <c r="E94" s="3">
         <v>59900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>113200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-31200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-57000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-90900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-37200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-258800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-41900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-35400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-31600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-29100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-69800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-35700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-19300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>311500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>6300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>57800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-19400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>219500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-516400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>120600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-296800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-5400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-31200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-82500</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7900,7 +8133,7 @@
         <v>-69400</v>
       </c>
       <c r="G96" s="3">
-        <v>-69300</v>
+        <v>-69400</v>
       </c>
       <c r="H96" s="3">
         <v>-69300</v>
@@ -7912,64 +8145,64 @@
         <v>-69300</v>
       </c>
       <c r="K96" s="3">
+        <v>-69300</v>
+      </c>
+      <c r="L96" s="3">
         <v>-68600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-66300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-64800</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-63200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-62600</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-61700</v>
       </c>
       <c r="Q96" s="3">
         <v>-61700</v>
       </c>
       <c r="R96" s="3">
+        <v>-61700</v>
+      </c>
+      <c r="S96" s="3">
         <v>-92400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-88200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-85500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-81500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-80300</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-80200</v>
       </c>
       <c r="X96" s="3">
         <v>-80200</v>
       </c>
       <c r="Y96" s="3">
+        <v>-80200</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-81900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-82800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-95300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-26100</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-30700</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-30000</v>
       </c>
       <c r="AE96" s="3">
         <v>-30000</v>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>-30000</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>-30000</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-136400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-68500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-196100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-13500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-91600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>56000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-112500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-274600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>371600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-69300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-60100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-60400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-90500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>8900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-50400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-83500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-424800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-87500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-212800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-138400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-161800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-114400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>341000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>317900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-16700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-43300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-100</v>
-      </c>
-      <c r="M101" s="3">
-        <v>100</v>
       </c>
       <c r="N101" s="3">
         <v>100</v>
       </c>
       <c r="O101" s="3">
+        <v>100</v>
+      </c>
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-200</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>-700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E102" s="3">
         <v>6500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-6300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-15200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>22800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-40400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>42200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-86600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-435500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>477500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>44400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-36000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>23700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>5000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-25600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>13300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>9500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-17800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>24800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-27000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-79900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-86100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>167500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-529300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>544100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>20700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-12700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>6000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-84200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBRA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBRA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>SBRA</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>166700</v>
+      </c>
+      <c r="E8" s="3">
         <v>163400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>161600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>161200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>161300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>165000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>140800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>156000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>163100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>135700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>128600</v>
-      </c>
-      <c r="N8" s="3">
-        <v>152400</v>
       </c>
       <c r="O8" s="3">
         <v>152400</v>
       </c>
       <c r="P8" s="3">
+        <v>152400</v>
+      </c>
+      <c r="Q8" s="3">
         <v>151500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>142100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>153900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>149300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>155800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>149800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>152500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>136800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>139200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>151800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>166300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>166100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>166500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>111800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>64700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>62700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>61800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>61900</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E9" s="3">
         <v>45200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>44500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>44000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>43600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>39200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>36700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>34000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>33100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>30900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>30000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>28500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>28000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>26900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>26300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>27000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>26000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>24000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>24200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>12000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>12500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>12600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>12100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>5900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2400</v>
-      </c>
-      <c r="AF9" s="3">
-        <v>1400</v>
       </c>
       <c r="AG9" s="3">
         <v>1400</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>117000</v>
+      </c>
+      <c r="E10" s="3">
         <v>118200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>117100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>117200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>117700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>125800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>104100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>122000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>130000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>104800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>98600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>123900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>124400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>124600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>115600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>127600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>122300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>129800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>125800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>128300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>124800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>126700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>139200</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>154000</v>
       </c>
       <c r="AA10" s="3">
         <v>154000</v>
       </c>
       <c r="AB10" s="3">
+        <v>154000</v>
+      </c>
+      <c r="AC10" s="3">
         <v>160600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>106700</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>60300</v>
       </c>
       <c r="AE10" s="3">
         <v>60300</v>
       </c>
       <c r="AF10" s="3">
+        <v>60300</v>
+      </c>
+      <c r="AG10" s="3">
         <v>60400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,92 +1318,95 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E14" s="3">
         <v>7300</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>8600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>21200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>61000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-2000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>43400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2200</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>1700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>6000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>8300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>14600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-45100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>103100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>2900</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>600</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
@@ -1396,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1405,40 +1428,40 @@
         <v>42900</v>
       </c>
       <c r="E15" s="3">
+        <v>42900</v>
+      </c>
+      <c r="F15" s="3">
         <v>43200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>44100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>52800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>49900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>47400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>45200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>45300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>45100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>45000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>44500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>44400</v>
-      </c>
-      <c r="P15" s="3">
-        <v>44200</v>
       </c>
       <c r="Q15" s="3">
         <v>44200</v>
@@ -1450,49 +1473,52 @@
         <v>44200</v>
       </c>
       <c r="T15" s="3">
+        <v>44200</v>
+      </c>
+      <c r="U15" s="3">
         <v>44000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>43100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>49500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>44900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>48100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>48500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>46800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>48000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>51600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>25900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>17200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>19100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>17200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>140200</v>
+      </c>
+      <c r="E17" s="3">
         <v>144300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>131300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>131200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>148100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>153900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>186800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>129700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>117200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>160300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>115200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>110900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>114700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>111800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>114000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>112000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>111500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>116500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>125300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>67000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>211100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>141700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>115500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>105500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>105900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>109500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>97500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>49000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>45800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>40800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E18" s="3">
         <v>19100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>30300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>30000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>13200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>11100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-46000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>26300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>45900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-24600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>41500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>37700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>39700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>28100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>41900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>37800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>39300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>24500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>85500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-74300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>36300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>60800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>60200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>57000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>14300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>15700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>16900</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>21000</v>
       </c>
       <c r="AG18" s="3">
         <v>21000</v>
       </c>
-    </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,198 +1781,205 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-44900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-8500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-22000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-96000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-9200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-173500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-11900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-15700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>140600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>2800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>47400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>5000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>69600</v>
+      </c>
+      <c r="E21" s="3">
         <v>60500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>28600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>65700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>44100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-34900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-2100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>62200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>86100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>21300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>55400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-87600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>78500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>80600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>80500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>74300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>80400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>84900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>67200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>134000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-32100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>29900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>84400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>248200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>111000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>155400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>41400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>37900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>38100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>40600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2033,103 +2073,109 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E23" s="3">
         <v>17600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-14600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-84800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-49500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>17100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>40900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-23800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>10300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-132100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>34100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>36500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>36300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>30100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>36300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>40900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>24100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>84500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-77100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-18200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>36000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>201400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>63000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>104500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>14900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>20700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>19000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>23400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2140,91 +2186,94 @@
         <v>500</v>
       </c>
       <c r="F24" s="3">
+        <v>500</v>
+      </c>
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>600</v>
-      </c>
-      <c r="J24" s="3">
-        <v>300</v>
       </c>
       <c r="K24" s="3">
         <v>300</v>
       </c>
       <c r="L24" s="3">
+        <v>300</v>
+      </c>
+      <c r="M24" s="3">
         <v>500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>600</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>500</v>
       </c>
       <c r="AB24" s="3">
         <v>500</v>
       </c>
       <c r="AC24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AD24" s="3">
         <v>-200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E26" s="3">
         <v>17200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-15100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>21200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-84900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-50100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>16800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>40600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-24400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-132600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>33400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>37100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>36500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>29600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>35200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>39700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>23300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>83700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-77700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-19400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>35200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>200800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>62500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>104000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>15100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>20500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>18800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>23200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E27" s="3">
         <v>17200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-15100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>21200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-84900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-50100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>40600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-24400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>10200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-132600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>33400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>37100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>36500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>29600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>35200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>39700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>23300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>83700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-77700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-19400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>35200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>193600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>59900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>101400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>12500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>18000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>16300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>20600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E32" s="3">
         <v>1500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>44900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>8500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>22000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>96000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>9200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>173500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>11900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>15700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-140600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-47400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E33" s="3">
         <v>17200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-15100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>21200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-84900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-50100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>40600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-24400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-132600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>33400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>37100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>36500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>29600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>35200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>39700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>23300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>83700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-77700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-19400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>35200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>193600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>59900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>101400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>12500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>18000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>16300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>20600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E35" s="3">
         <v>17200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-15100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>21200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-84900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-50100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>40600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-24400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-132600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>33400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>37100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>36500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>29600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>35200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>39700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>23300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>83700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-77700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-19400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>35200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>193600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>59900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>101400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>12500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>18000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>16300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>20600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>59900</v>
+      </c>
+      <c r="E41" s="3">
         <v>41300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>33300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>27200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>33500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>49300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>26300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>67200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>24800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>112000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>546300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>69300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>59100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>35000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>28300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>54100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>39100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>29400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>47600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>22900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>50200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>36300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>38800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>46400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>518600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>30900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>13200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>12800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>25700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3628,8 +3718,11 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3723,8 +3816,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,8 +3914,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3895,26 +3994,29 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>8</v>
+      <c r="AB45" s="3">
+        <v>0</v>
       </c>
       <c r="AC45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AD45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE45" s="3">
         <v>141200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>126000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>125300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>116400</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4008,281 +4110,290 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>554500</v>
+      </c>
+      <c r="E47" s="3">
         <v>557500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>553700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>557400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>548500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>546400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>597900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>615300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>491000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>495800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>215800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>219200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>385000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>391600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>397600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>379700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>400100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>426800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>432600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>439400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>444900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>453800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>454700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>456200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>455800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>114400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>149800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>94200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>96500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>96000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>94500</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4588700</v>
+      </c>
+      <c r="E48" s="3">
         <v>4617300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4603000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4751900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4797000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4959300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5018900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5045100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5156100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5162900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5228700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5269400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5279400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5285000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5306300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5358500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5363200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5350700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5354400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5388400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5447200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5853500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5975600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5993700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6108800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5994400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5972800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1995900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1993600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>2009900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1999800</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E49" s="3">
         <v>30900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>32700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>36000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>39400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>40100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>48300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>49800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>52900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>54100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>76400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>79700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>81500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>82800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>85900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>93500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>96800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>101500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>105000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>108900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>119700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>131100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>142900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>156300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>161400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>167100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>262800</v>
-      </c>
-      <c r="AD49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE49" s="3" t="s">
         <v>8</v>
@@ -4293,8 +4404,11 @@
       <c r="AG49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E52" s="3">
         <v>5400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4900</v>
-      </c>
-      <c r="J52" s="3">
-        <v>4400</v>
       </c>
       <c r="K52" s="3">
         <v>4400</v>
       </c>
       <c r="L52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="M52" s="3">
         <v>3900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>5100</v>
-      </c>
-      <c r="N52" s="3">
-        <v>4600</v>
       </c>
       <c r="O52" s="3">
         <v>4600</v>
       </c>
       <c r="P52" s="3">
+        <v>4600</v>
+      </c>
+      <c r="Q52" s="3">
         <v>6400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>10000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>9900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>280500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>103200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>186800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>11800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>68800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>12500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>9400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>11200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5374400</v>
+      </c>
+      <c r="E54" s="3">
         <v>5386200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5380600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5524300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5556300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5747700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5844900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5961400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5884900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5966700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6209500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5822100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5963800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5985600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5991600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6023600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6092300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6069300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6068000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6123200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6455100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6665300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6910300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7028100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6984600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7032300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6588300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2254000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2240100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2265900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2239400</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,103 +4968,107 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>79100</v>
+      </c>
+      <c r="E57" s="3">
         <v>120500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>106900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>105500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>121600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>124100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>123200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>101100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>92900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>121500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>108600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>103300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>105900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>130200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>125600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>143300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>112500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>98400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>92100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>90800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>72900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>94800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>86900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>105300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>102400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>102500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>116100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>37100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>33400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>39600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5028,61 +5162,64 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>33700</v>
+      </c>
+      <c r="E59" s="3">
         <v>16500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>18200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>22000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>16600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>25400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>16100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>17600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18100</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T59" s="3">
-        <v>9800</v>
+      <c r="T59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U59" s="3">
         <v>9800</v>
@@ -5091,16 +5228,16 @@
         <v>9800</v>
       </c>
       <c r="W59" s="3">
+        <v>9800</v>
+      </c>
+      <c r="X59" s="3">
         <v>10000</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z59" s="3">
-        <v>0</v>
+      <c r="Z59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA59" s="3">
         <v>0</v>
@@ -5123,8 +5260,11 @@
       <c r="AG59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5218,103 +5358,109 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2463400</v>
+      </c>
+      <c r="E61" s="3">
         <v>2414100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2349500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2420000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2396600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2506800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2446900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2480200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2357500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2394500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2702100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2266300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2281600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2372400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2423000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2455300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2479300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2402100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2603100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2686000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3230200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3232000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3368600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3423800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3361100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3394500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3005500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1220100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1202400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1210700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1187400</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5408,8 +5554,11 @@
       <c r="AG62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2607300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2583600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2511700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2580600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2580100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2691300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2636200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2643700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2523400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2587200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2880400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2439100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2460400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2576400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2627300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2662300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2697100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2580800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2785600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2867100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3408700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3414900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3547400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3624600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3562400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3599500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3219200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1257300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1235800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1250300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1225600</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6088,7 +6256,7 @@
         <v>0</v>
       </c>
       <c r="AA70" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB70" s="3">
         <v>100</v>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1762000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1718300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1665000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1579900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1531200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1451900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1296900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1177000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1124100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1095200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1001200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-944500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-746500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-716200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-689800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-663900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-631300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-573300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-523700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-460800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-462600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-271600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-171100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-125600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-238600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-217200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-225500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-214100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-203600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-192200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-185000</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2767200</v>
+      </c>
+      <c r="E76" s="3">
         <v>2802500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2868900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2943700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2976200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3056400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3208700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3317700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3361500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3379500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3329100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3383100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3503400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3409200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3364300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3361300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3395200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3488500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3282400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3256100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3046500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3250400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3362900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3403500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3422100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3432700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3369000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>996600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1004300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1015500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1013800</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E81" s="3">
         <v>17200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-15100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>21200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-84900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-50100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>40600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-24400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-132600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>33400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>37100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>36500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>29600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>35200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>39700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>23300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>83700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-77700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-19400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>35200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>193600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>59900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>101400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>12500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>18000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>16300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>20600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,8 +7201,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7012,40 +7211,40 @@
         <v>42900</v>
       </c>
       <c r="E83" s="3">
+        <v>42900</v>
+      </c>
+      <c r="F83" s="3">
         <v>43200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>44100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>52800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>49900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>47400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>45200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>45300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>45100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>45000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>44500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>44400</v>
-      </c>
-      <c r="P83" s="3">
-        <v>44200</v>
       </c>
       <c r="Q83" s="3">
         <v>44200</v>
@@ -7057,49 +7256,52 @@
         <v>44200</v>
       </c>
       <c r="T83" s="3">
+        <v>44200</v>
+      </c>
+      <c r="U83" s="3">
         <v>44000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>43100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>49500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>44900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>48100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>48500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>46800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>48000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>51000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>26600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>17200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>19100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>17200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>52800</v>
+      </c>
+      <c r="E89" s="3">
         <v>78700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>83200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>70300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>68300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>67600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>108500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>76600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>63100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>97900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>106200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>83700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>68500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>89400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>96900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>93800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>74800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>95500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>85100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>137900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>54000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>77600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>71500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>109900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>101600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>82500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>22700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>31600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>42900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>39300</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,64 +7923,65 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
         <v>-38900</v>
       </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
       <c r="F91" s="3">
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-39600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-63400</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
         <v>-20600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-37300</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-33500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-28700</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-25700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-67300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-36200</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>8</v>
@@ -7768,38 +7989,41 @@
       <c r="W91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-22500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-25000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-61800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>59900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>113200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-31200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-57000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-90900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-37200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-258800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-41900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-35400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-31600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-29100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-69800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-35700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-19300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>311500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>6300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>57800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-19400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>219500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-516400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>120600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-296800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-31200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-82500</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8136,7 +8370,7 @@
         <v>-69400</v>
       </c>
       <c r="H96" s="3">
-        <v>-69300</v>
+        <v>-69400</v>
       </c>
       <c r="I96" s="3">
         <v>-69300</v>
@@ -8148,64 +8382,64 @@
         <v>-69300</v>
       </c>
       <c r="L96" s="3">
+        <v>-69300</v>
+      </c>
+      <c r="M96" s="3">
         <v>-68600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-66300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-64800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-63200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-62600</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-61700</v>
       </c>
       <c r="R96" s="3">
         <v>-61700</v>
       </c>
       <c r="S96" s="3">
+        <v>-61700</v>
+      </c>
+      <c r="T96" s="3">
         <v>-92400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-88200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-85500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-81500</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-80300</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-80200</v>
       </c>
       <c r="Y96" s="3">
         <v>-80200</v>
       </c>
       <c r="Z96" s="3">
+        <v>-80200</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-81900</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-82800</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-95300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-26100</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-30700</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-30000</v>
       </c>
       <c r="AF96" s="3">
         <v>-30000</v>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>-30000</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>-30000</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-136400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-68500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-196100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-13500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-91600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>56000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-112500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-274600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>371600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-69300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-60100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-60400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-90500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>8900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-50400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-83500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-424800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-87500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-212800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-138400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-161800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-114400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>341000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>317900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-16700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-43300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
-      </c>
-      <c r="N101" s="3">
-        <v>100</v>
       </c>
       <c r="O101" s="3">
         <v>100</v>
       </c>
       <c r="P101" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q101" s="3">
         <v>300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-200</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>100</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>-700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E102" s="3">
         <v>7900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>6500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-6300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-15200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>22800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-40400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>42200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-86600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-435500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>477500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>44400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-36000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>23700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>5000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-25600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>13300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>9500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-17800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>24800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-27000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-79900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-86100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>167500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-529300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>544100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>20700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-12700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>6000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-84200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBRA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBRA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>SBRA</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>176100</v>
+      </c>
+      <c r="E8" s="3">
         <v>166700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>163400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>161600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>161200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>161300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>165000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>140800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>156000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>163100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>135700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>128600</v>
-      </c>
-      <c r="O8" s="3">
-        <v>152400</v>
       </c>
       <c r="P8" s="3">
         <v>152400</v>
       </c>
       <c r="Q8" s="3">
+        <v>152400</v>
+      </c>
+      <c r="R8" s="3">
         <v>151500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>142100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>153900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>149300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>155800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>149800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>152500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>136800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>139200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>151800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>166300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>166100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>166500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>111800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>64700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>62700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>61800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>61900</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E9" s="3">
         <v>49700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>45200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>44500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>44000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>43600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>39200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>36700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>34000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>33100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>30900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>30000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>28500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>28000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>26900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>26500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>26300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>27000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>26000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>24000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>24200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>12000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>12500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>12300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>12100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2400</v>
-      </c>
-      <c r="AG9" s="3">
-        <v>1400</v>
       </c>
       <c r="AH9" s="3">
         <v>1400</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>125700</v>
+      </c>
+      <c r="E10" s="3">
         <v>117000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>118200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>117100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>117200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>117700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>125800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>104100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>122000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>130000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>104800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>98600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>123900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>124400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>124600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>115600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>127600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>122300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>129800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>125800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>128300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>124800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>126700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>139200</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>154000</v>
       </c>
       <c r="AB10" s="3">
         <v>154000</v>
       </c>
       <c r="AC10" s="3">
+        <v>154000</v>
+      </c>
+      <c r="AD10" s="3">
         <v>160600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>106700</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>60300</v>
       </c>
       <c r="AF10" s="3">
         <v>60300</v>
       </c>
       <c r="AG10" s="3">
+        <v>60300</v>
+      </c>
+      <c r="AH10" s="3">
         <v>60400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,95 +1338,98 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E14" s="3">
         <v>3100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7300</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>8600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>21200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>61000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>11700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-2000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>43400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2200</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>6000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>8300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>14600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-45100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>103100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2900</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>500</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>600</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
@@ -1419,52 +1439,55 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>42900</v>
+        <v>41700</v>
       </c>
       <c r="E15" s="3">
         <v>42900</v>
       </c>
       <c r="F15" s="3">
+        <v>42900</v>
+      </c>
+      <c r="G15" s="3">
         <v>43200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>44100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>52800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>49900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>47400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>45200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>45300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>45100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>45000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>44500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>44400</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>44200</v>
       </c>
       <c r="R15" s="3">
         <v>44200</v>
@@ -1476,49 +1499,52 @@
         <v>44200</v>
       </c>
       <c r="U15" s="3">
+        <v>44200</v>
+      </c>
+      <c r="V15" s="3">
         <v>44000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>43100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>49500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>44900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>48100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>48500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>46800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>48000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>51600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>25900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>17200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>19100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>17200</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>153700</v>
+      </c>
+      <c r="E17" s="3">
         <v>140200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>144300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>131300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>131200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>148100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>153900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>186800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>129700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>117200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>160300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>115200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>110900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>114700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>111800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>114000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>112000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>111500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>116500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>125300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>67000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>211100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>141700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>115500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>105500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>105900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>109500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>97500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>49000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>45800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>40800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E18" s="3">
         <v>26500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>19100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>30300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>30000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-46000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>26300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>45900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-24600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>13400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>41500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>37700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>39700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>28100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>41900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>37800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>39300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>24500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>85500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-74300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>36300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>60800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>60200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>57000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>14300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>15700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>16900</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>21000</v>
       </c>
       <c r="AH18" s="3">
         <v>21000</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,204 +1815,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-44900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-8500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-22000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-96000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-9200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-173500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>8200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-11900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>140600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>2800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>47400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>5000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>66100</v>
+      </c>
+      <c r="E21" s="3">
         <v>69600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>60500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>28600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>65700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>44100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-34900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-2100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>62200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>86100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>21300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>55400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-87600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>78500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>80600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>80500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>74300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>80400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>84900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>67200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>134000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-32100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>29900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>84400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>248200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>111000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>155400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>41400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>37900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>38100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>40600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2076,111 +2116,117 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E23" s="3">
         <v>26700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>17600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-14600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>21500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-84800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-49500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>17100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>40900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-23800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>10300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-132100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>34100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>36500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>36300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>30100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>36300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>40900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>24100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>84500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-77100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-18200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>36000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>201400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>63000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>104500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>14900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>20700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>19000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>23400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E24" s="3">
         <v>500</v>
@@ -2189,91 +2235,94 @@
         <v>500</v>
       </c>
       <c r="G24" s="3">
+        <v>500</v>
+      </c>
+      <c r="H24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>600</v>
-      </c>
-      <c r="K24" s="3">
-        <v>300</v>
       </c>
       <c r="L24" s="3">
         <v>300</v>
       </c>
       <c r="M24" s="3">
+        <v>300</v>
+      </c>
+      <c r="N24" s="3">
         <v>500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>600</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>500</v>
       </c>
       <c r="AC24" s="3">
         <v>500</v>
       </c>
       <c r="AD24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AE24" s="3">
         <v>-200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E26" s="3">
         <v>26300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>17200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-15100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>21200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-84900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-50100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>16800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>40600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-24400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-132600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>33400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>37100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>36500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>29600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>35200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>39700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>23300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>83700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-77700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-19400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>35200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>200800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>62500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>104000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>15100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>20500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>18800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>23200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E27" s="3">
         <v>26300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>17200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-15100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>21200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-84900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-50100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>16800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>40600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-24400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-132600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>33400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>37100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>36500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>29600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>35200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>39700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>23300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>83700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-77700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-19400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>35200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>193600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>59900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>101400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>12500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>18000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>16300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>20600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>44900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>8500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>22000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>96000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>9200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>173500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-8200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>11900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>15700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-140600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-47400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E33" s="3">
         <v>26300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>17200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-15100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>21200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-84900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-50100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>16800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>40600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-24400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-132600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>33400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>37100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>36500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>29600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>35200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>39700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>23300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>83700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-77700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-19400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>35200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>193600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>59900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>101400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>12500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>18000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>16300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>20600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E35" s="3">
         <v>26300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>17200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-15100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>21200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-84900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-50100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>16800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>40600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-24400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-132600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>33400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>37100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>36500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>29600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>35200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>39700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>23300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>83700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-77700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-19400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>35200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>193600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>59900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>101400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>12500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>18000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>16300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>20600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>36400</v>
+      </c>
+      <c r="E41" s="3">
         <v>59900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>41300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>33300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>27200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>49300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>26300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>67200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>24800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>112000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>546300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>69300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>24900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>59100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>35000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>28300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>54100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>39100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>29400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>47600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>22900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>50200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>36300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>38800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>46400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>518600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>30900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>13200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>12800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>25700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,8 +3811,11 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3997,26 +4096,29 @@
       <c r="AB45" s="3">
         <v>0</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>8</v>
+      <c r="AC45" s="3">
+        <v>0</v>
       </c>
       <c r="AD45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AE45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF45" s="3">
         <v>141200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>126000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>125300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>116400</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4113,290 +4215,299 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>568800</v>
+      </c>
+      <c r="E47" s="3">
         <v>554500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>557500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>553700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>557400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>548500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>546400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>597900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>615300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>491000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>495800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>215800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>219200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>385000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>391600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>397600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>379700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>400100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>426800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>432600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>439400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>444900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>453800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>454700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>456200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>455800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>114400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>149800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>94200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>96500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>96000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>94500</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4576900</v>
+      </c>
+      <c r="E48" s="3">
         <v>4588700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4617300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4603000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4751900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4797000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4959300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5018900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5045100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5156100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5162900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5228700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5269400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5279400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5285000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5306300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5358500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5363200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5350700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5354400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5388400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5447200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5853500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5975600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5993700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6108800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5994400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5972800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1995900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1993600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2009900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1999800</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E49" s="3">
         <v>28300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>30900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>32700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>36000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>39400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>40100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>48300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>49800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>52900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>54100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>76400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>79700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>81500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>82800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>85900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>93500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>96800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>101500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>105000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>108900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>119700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>131100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>142900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>156300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>161400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>167100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>262800</v>
-      </c>
-      <c r="AE49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF49" s="3" t="s">
         <v>8</v>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E52" s="3">
         <v>6000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>5200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4900</v>
-      </c>
-      <c r="K52" s="3">
-        <v>4400</v>
       </c>
       <c r="L52" s="3">
         <v>4400</v>
       </c>
       <c r="M52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="N52" s="3">
         <v>3900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>5100</v>
-      </c>
-      <c r="O52" s="3">
-        <v>4600</v>
       </c>
       <c r="P52" s="3">
         <v>4600</v>
       </c>
       <c r="Q52" s="3">
+        <v>4600</v>
+      </c>
+      <c r="R52" s="3">
         <v>6400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>10000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>10200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>9900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>280500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>103200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>186800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>11800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>68800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>12500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>11200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>9000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5351100</v>
+      </c>
+      <c r="E54" s="3">
         <v>5374400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5386200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5380600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5524300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5556300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5747700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5844900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5961400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5884900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5966700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6209500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5822100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5963800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5985600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5991600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6023600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6092300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6069300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6068000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6123200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6455100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6665300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6910300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7028100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6984600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7032300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6588300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2254000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2240100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2265900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2239400</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,106 +5099,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>83200</v>
+      </c>
+      <c r="E57" s="3">
         <v>79100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>120500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>106900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>105500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>121600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>124100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>123200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>101100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>92900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>121500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>108600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>103300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>105900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>130200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>125600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>143300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>112500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>98400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>92100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>90800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>72900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>94800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>86900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>105300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>102400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>102500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>116100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>37100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>33400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>39600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5165,64 +5299,67 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E59" s="3">
         <v>33700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>21400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>18200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>22000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>25400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>18200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18100</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U59" s="3">
-        <v>9800</v>
+      <c r="U59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V59" s="3">
         <v>9800</v>
@@ -5231,16 +5368,16 @@
         <v>9800</v>
       </c>
       <c r="X59" s="3">
+        <v>9800</v>
+      </c>
+      <c r="Y59" s="3">
         <v>10000</v>
-      </c>
-      <c r="Y59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA59" s="3">
-        <v>0</v>
+      <c r="AA59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB59" s="3">
         <v>0</v>
@@ -5263,8 +5400,11 @@
       <c r="AH59" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5361,106 +5501,112 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2446600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2463400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2414100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2349500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2420000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2396600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2506800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2446900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2480200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2357500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2394500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2702100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2266300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2281600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2372400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2423000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2455300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2479300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2402100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2603100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2686000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3230200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3232000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3368600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3423800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3361100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3394500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3005500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1220100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1202400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1210700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1187400</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2589100</v>
+      </c>
+      <c r="E66" s="3">
         <v>2607300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2583600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2511700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2580600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2580100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2691300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2636200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2643700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2523400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2587200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2880400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2439100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2460400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2576400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2627300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2662300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2697100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2580800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2785600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2867100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3408700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3414900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3547400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3624600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3562400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3599500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3219200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1257300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1235800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1250300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1225600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6259,7 +6427,7 @@
         <v>0</v>
       </c>
       <c r="AB70" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC70" s="3">
         <v>100</v>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1808200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1762000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1718300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1665000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1579900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1531200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1451900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1296900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1177000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1124100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1095200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1001200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-944500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-746500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-716200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-689800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-663900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-631300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-573300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-523700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-460800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-462600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-271600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-171100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-125600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-238600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-217200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-225500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-214100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-203600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-192200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-185000</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2762000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2767200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2802500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2868900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2943700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2976200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3056400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3208700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3317700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3361500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3379500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3329100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3383100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3503400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3409200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3364300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3361300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3395200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3488500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3282400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3256100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3046500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3250400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3362900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3403500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3422100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3432700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3369000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>996600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1004300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1015500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1013800</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E81" s="3">
         <v>26300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>17200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-15100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>21200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-84900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-50100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>16800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>40600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-24400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-132600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>33400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>37100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>36500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>29600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>35200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>39700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>23300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>83700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-77700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-19400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>35200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>193600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>59900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>101400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>12500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>18000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>16300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>20600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,52 +7400,53 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>42900</v>
+        <v>41700</v>
       </c>
       <c r="E83" s="3">
         <v>42900</v>
       </c>
       <c r="F83" s="3">
+        <v>42900</v>
+      </c>
+      <c r="G83" s="3">
         <v>43200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>44100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>52800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>49900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>47400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>45200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>45300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>45100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>45000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>44500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>44400</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>44200</v>
       </c>
       <c r="R83" s="3">
         <v>44200</v>
@@ -7259,49 +7458,52 @@
         <v>44200</v>
       </c>
       <c r="U83" s="3">
+        <v>44200</v>
+      </c>
+      <c r="V83" s="3">
         <v>44000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>43100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>49500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>44900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>48100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>48500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>46800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>48000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>51000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>26600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>17200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>19100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>17200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>80100</v>
+      </c>
+      <c r="E89" s="3">
         <v>52800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>78700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>83200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>70300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>68300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>67600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>108500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>76600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>63100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>97900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>106200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>83700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>68500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>89400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>96900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>93800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>74800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>95500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>85100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>137900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>54000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>77600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>71500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>109900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>101600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>82500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>22700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>31600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>42900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>39300</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,67 +8144,68 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>0</v>
+        <v>-36100</v>
       </c>
       <c r="E91" s="3">
+        <v>0</v>
+      </c>
+      <c r="F91" s="3">
         <v>-38900</v>
       </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
       <c r="G91" s="3">
         <v>0</v>
       </c>
       <c r="H91" s="3">
+        <v>0</v>
+      </c>
+      <c r="I91" s="3">
         <v>-39600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-63400</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
         <v>-20600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-37300</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-33500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-28700</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-25700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-67300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-36200</v>
-      </c>
-      <c r="V91" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>8</v>
@@ -7992,38 +8213,41 @@
       <c r="X91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Y91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-22500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-25000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-100</v>
       </c>
-      <c r="AH91" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-57300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-61800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>59900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>113200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-31200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-57000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-90900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-37200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-258800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-41900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-35400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-31600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-29100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-69800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-35700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-19300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>311500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>6300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>57800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-19400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>219500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-516400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>120600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-296800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-31200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-82500</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,13 +8585,14 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-69400</v>
+        <v>-69500</v>
       </c>
       <c r="E96" s="3">
         <v>-69400</v>
@@ -8373,7 +8607,7 @@
         <v>-69400</v>
       </c>
       <c r="I96" s="3">
-        <v>-69300</v>
+        <v>-69400</v>
       </c>
       <c r="J96" s="3">
         <v>-69300</v>
@@ -8385,64 +8619,64 @@
         <v>-69300</v>
       </c>
       <c r="M96" s="3">
+        <v>-69300</v>
+      </c>
+      <c r="N96" s="3">
         <v>-68600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-66300</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-64800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-63200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-62600</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-61700</v>
       </c>
       <c r="S96" s="3">
         <v>-61700</v>
       </c>
       <c r="T96" s="3">
+        <v>-61700</v>
+      </c>
+      <c r="U96" s="3">
         <v>-92400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-88200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-85500</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-81500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-80300</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-80200</v>
       </c>
       <c r="Z96" s="3">
         <v>-80200</v>
       </c>
       <c r="AA96" s="3">
+        <v>-80200</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-81900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-82800</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-95300</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-26100</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-30700</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-30000</v>
       </c>
       <c r="AG96" s="3">
         <v>-30000</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>-30000</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>-30000</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-46400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-20200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-9400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-136400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-68500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-196100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-13500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-91600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>56000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-112500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-274600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>371600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-69300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-60100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-60400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-90500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>8900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-50400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-83500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-424800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-87500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-212800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-138400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-161800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-114400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>341000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>317900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-16700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-43300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-100</v>
-      </c>
-      <c r="O101" s="3">
-        <v>100</v>
       </c>
       <c r="P101" s="3">
         <v>100</v>
       </c>
       <c r="Q101" s="3">
+        <v>100</v>
+      </c>
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-200</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>-700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-23600</v>
+      </c>
+      <c r="E102" s="3">
         <v>19200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>22800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-40400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>42200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-86600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-435500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>477500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>44400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-36000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>23700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>5000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-25600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>13300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>9500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-17800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>24800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-27000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-79900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-86100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>167500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-529300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>544100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>20700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-12700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>6000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-84200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBRA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBRA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
   <si>
     <t>SBRA</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>176100</v>
+        <v>178200</v>
       </c>
       <c r="E8" s="3">
-        <v>166700</v>
+        <v>176200</v>
       </c>
       <c r="F8" s="3">
-        <v>163400</v>
+        <v>166200</v>
       </c>
       <c r="G8" s="3">
-        <v>161600</v>
+        <v>162600</v>
       </c>
       <c r="H8" s="3">
-        <v>161200</v>
+        <v>161000</v>
       </c>
       <c r="I8" s="3">
-        <v>161300</v>
+        <v>160500</v>
       </c>
       <c r="J8" s="3">
+        <v>160500</v>
+      </c>
+      <c r="K8" s="3">
         <v>165000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>140800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>156000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>163100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>135700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>128600</v>
-      </c>
-      <c r="P8" s="3">
-        <v>152400</v>
       </c>
       <c r="Q8" s="3">
         <v>152400</v>
       </c>
       <c r="R8" s="3">
+        <v>152400</v>
+      </c>
+      <c r="S8" s="3">
         <v>151500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>142100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>153900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>149300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>155800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>149800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>152500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>136800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>139200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>151800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>166300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>166100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>166500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>111800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>64700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>62700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>61800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>61900</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>50400</v>
+        <v>58400</v>
       </c>
       <c r="E9" s="3">
-        <v>49700</v>
+        <v>54600</v>
       </c>
       <c r="F9" s="3">
-        <v>45200</v>
+        <v>53900</v>
       </c>
       <c r="G9" s="3">
-        <v>44500</v>
+        <v>49500</v>
       </c>
       <c r="H9" s="3">
-        <v>44000</v>
+        <v>49200</v>
       </c>
       <c r="I9" s="3">
-        <v>43600</v>
+        <v>49200</v>
       </c>
       <c r="J9" s="3">
+        <v>47600</v>
+      </c>
+      <c r="K9" s="3">
         <v>39200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>36700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>34000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>33100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>30900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>30000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>28500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>28000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>26900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>26500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>26300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>27000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>26000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>24000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>24200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>12000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>12600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>12300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>12100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2400</v>
-      </c>
-      <c r="AH9" s="3">
-        <v>1400</v>
       </c>
       <c r="AI9" s="3">
         <v>1400</v>
       </c>
+      <c r="AJ9" s="3">
+        <v>1400</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>125700</v>
+        <v>119900</v>
       </c>
       <c r="E10" s="3">
-        <v>117000</v>
+        <v>121600</v>
       </c>
       <c r="F10" s="3">
-        <v>118200</v>
+        <v>112300</v>
       </c>
       <c r="G10" s="3">
-        <v>117100</v>
+        <v>113100</v>
       </c>
       <c r="H10" s="3">
-        <v>117200</v>
+        <v>111800</v>
       </c>
       <c r="I10" s="3">
-        <v>117700</v>
+        <v>111300</v>
       </c>
       <c r="J10" s="3">
+        <v>112900</v>
+      </c>
+      <c r="K10" s="3">
         <v>125800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>104100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>122000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>130000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>104800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>98600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>123900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>124400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>124600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>115600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>127600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>122300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>129800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>125800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>128300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>124800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>126700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>139200</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>154000</v>
       </c>
       <c r="AC10" s="3">
         <v>154000</v>
       </c>
       <c r="AD10" s="3">
+        <v>154000</v>
+      </c>
+      <c r="AE10" s="3">
         <v>160600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>106700</v>
-      </c>
-      <c r="AF10" s="3">
-        <v>60300</v>
       </c>
       <c r="AG10" s="3">
         <v>60300</v>
       </c>
       <c r="AH10" s="3">
+        <v>60300</v>
+      </c>
+      <c r="AI10" s="3">
         <v>60400</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,98 +1358,101 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>15300</v>
+        <v>5700</v>
       </c>
       <c r="E14" s="3">
-        <v>3100</v>
+        <v>13600</v>
       </c>
       <c r="F14" s="3">
-        <v>7300</v>
+        <v>2200</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>42300</v>
       </c>
       <c r="I14" s="3">
-        <v>8600</v>
+        <v>7800</v>
       </c>
       <c r="J14" s="3">
+        <v>29800</v>
+      </c>
+      <c r="K14" s="3">
         <v>21200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>61000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>11700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-2000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>43400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>1700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>6000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>8300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>14600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-45100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>103100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2900</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>500</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>600</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
@@ -1442,55 +1462,58 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E15" s="3">
         <v>41700</v>
-      </c>
-      <c r="E15" s="3">
-        <v>42900</v>
       </c>
       <c r="F15" s="3">
         <v>42900</v>
       </c>
       <c r="G15" s="3">
+        <v>42900</v>
+      </c>
+      <c r="H15" s="3">
         <v>43200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>44100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>52800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>49900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>47400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>45200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>45300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>45100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>45000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>44500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>44400</v>
-      </c>
-      <c r="R15" s="3">
-        <v>44200</v>
       </c>
       <c r="S15" s="3">
         <v>44200</v>
@@ -1502,49 +1525,52 @@
         <v>44200</v>
       </c>
       <c r="V15" s="3">
+        <v>44200</v>
+      </c>
+      <c r="W15" s="3">
         <v>44000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>43100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>49500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>44900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>48100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>48500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>46800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>48000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>51600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>25900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>17200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>19100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>17200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>153700</v>
+        <v>113500</v>
       </c>
       <c r="E17" s="3">
-        <v>140200</v>
+        <v>109000</v>
       </c>
       <c r="F17" s="3">
-        <v>144300</v>
+        <v>108700</v>
       </c>
       <c r="G17" s="3">
-        <v>131300</v>
+        <v>109100</v>
       </c>
       <c r="H17" s="3">
-        <v>131200</v>
+        <v>103200</v>
       </c>
       <c r="I17" s="3">
-        <v>148100</v>
+        <v>102800</v>
       </c>
       <c r="J17" s="3">
+        <v>110900</v>
+      </c>
+      <c r="K17" s="3">
         <v>153900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>186800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>129700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>117200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>160300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>115200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>110900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>114700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>111800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>114000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>112000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>111500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>116500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>125300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>67000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>211100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>141700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>115500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>105500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>105900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>109500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>97500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>49000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>45800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>40800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>22400</v>
+        <v>64700</v>
       </c>
       <c r="E18" s="3">
-        <v>26500</v>
+        <v>67200</v>
       </c>
       <c r="F18" s="3">
-        <v>19100</v>
+        <v>57500</v>
       </c>
       <c r="G18" s="3">
-        <v>30300</v>
+        <v>53600</v>
       </c>
       <c r="H18" s="3">
-        <v>30000</v>
+        <v>57800</v>
       </c>
       <c r="I18" s="3">
-        <v>13200</v>
+        <v>57700</v>
       </c>
       <c r="J18" s="3">
+        <v>49600</v>
+      </c>
+      <c r="K18" s="3">
         <v>11100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-46000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>26300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>45900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-24600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>41500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>37700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>39700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>28100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>41900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>37800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>39300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>24500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>85500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-74300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>36300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>60800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>60200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>57000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>14300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>15700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>16900</v>
-      </c>
-      <c r="AH18" s="3">
-        <v>21000</v>
       </c>
       <c r="AI18" s="3">
         <v>21000</v>
       </c>
+      <c r="AJ18" s="3">
+        <v>21000</v>
+      </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,233 +1849,240 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="3">
+        <v>100</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>2000</v>
       </c>
-      <c r="E20" s="3">
-        <v>200</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-44900</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-8500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-22000</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>-96000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-173500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>8200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-11900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-15700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>140600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>47400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>5000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>66100</v>
+        <v>107500</v>
       </c>
       <c r="E21" s="3">
-        <v>69600</v>
+        <v>109000</v>
       </c>
       <c r="F21" s="3">
-        <v>60500</v>
+        <v>100300</v>
       </c>
       <c r="G21" s="3">
-        <v>28600</v>
+        <v>96500</v>
       </c>
       <c r="H21" s="3">
-        <v>65700</v>
+        <v>99100</v>
       </c>
       <c r="I21" s="3">
-        <v>44100</v>
+        <v>101800</v>
       </c>
       <c r="J21" s="3">
+        <v>102400</v>
+      </c>
+      <c r="K21" s="3">
         <v>-34900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-2100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>62200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>86100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>21300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>55400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-87600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>78500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>80600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>80500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>74300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>80400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>84900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>67200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>134000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-32100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>29900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>84400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>248200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>111000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>155400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>41400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>37900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>38100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>40600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>29500</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>28400</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>27900</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>28200</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>28300</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>28500</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -2119,117 +2159,123 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E23" s="3">
         <v>24400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>26700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>17600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>21500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-84800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-49500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>17100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>40900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-23800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>10300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-132100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>34100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>36500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>36300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>30100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>36300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>40900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>24100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>84500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-77100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-18200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>36000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>201400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>63000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>104500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>14900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>20700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>19000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>23400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
-      </c>
-      <c r="E24" s="3">
-        <v>500</v>
       </c>
       <c r="F24" s="3">
         <v>500</v>
@@ -2238,91 +2284,94 @@
         <v>500</v>
       </c>
       <c r="H24" s="3">
+        <v>500</v>
+      </c>
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>600</v>
-      </c>
-      <c r="L24" s="3">
-        <v>300</v>
       </c>
       <c r="M24" s="3">
         <v>300</v>
       </c>
       <c r="N24" s="3">
+        <v>300</v>
+      </c>
+      <c r="O24" s="3">
         <v>500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>600</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>500</v>
       </c>
       <c r="AD24" s="3">
         <v>500</v>
       </c>
       <c r="AE24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AF24" s="3">
         <v>-200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E26" s="3">
         <v>24000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>26300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>17200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-15100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>21200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-84900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-50100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>16800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>40600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-24400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-132600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>33400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>37100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>36500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>29600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>35200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>39700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>23300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>83700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-77700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-19400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>35200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>200800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>62500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>104000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>15100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>20500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>18800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>23200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E27" s="3">
         <v>24000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>26300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>17200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-15100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>21200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-84900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-50100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>16800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>40600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-24400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-132600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>33400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>37100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>36500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>29600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>35200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>39700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>23300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>83700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-77700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-19400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>35200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>193600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>59900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>101400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>12500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>18000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>16300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>20600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-2000</v>
       </c>
-      <c r="E32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="F32" s="3">
-        <v>1500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>44900</v>
-      </c>
-      <c r="H32" s="3">
-        <v>8500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>22000</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>96000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>173500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-8200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>11900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>15700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-140600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-47400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E33" s="3">
         <v>24000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>26300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>17200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-15100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>21200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-84900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-50100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>16800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>40600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-24400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-132600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>33400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>37100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>36500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>29600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>35200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>39700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>23300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>83700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-77700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-19400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>35200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>193600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>59900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>101400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>12500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>18000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>16300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>20600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E35" s="3">
         <v>24000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>26300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>17200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-15100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>21200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-84900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-50100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>16800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>40600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-24400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-132600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>33400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>37100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>36500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>29600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>35200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>39700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>23300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>83700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-77700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-19400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>35200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>193600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>59900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>101400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>12500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>18000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>16300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>20600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,132 +3698,136 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E41" s="3">
         <v>36400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>59900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>41300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>33300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>27200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>33500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>49300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>26300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>67200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>24800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>112000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>546300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>69300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>24900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>59100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>35000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>28300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>54100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>39100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>29400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>47600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>22900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>50200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>36300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>38800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>46400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>518600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>30900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>13200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>12800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>25700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>10300</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>27100</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>18900</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>39300</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>31100</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>19800</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3814,31 +3904,34 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>46400</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>46100</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>43700</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>147100</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>42300</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>37400</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3915,31 +4008,34 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,31 +4112,34 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4099,49 +4198,52 @@
       <c r="AC45" s="3">
         <v>0</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>8</v>
+      <c r="AD45" s="3">
+        <v>0</v>
       </c>
       <c r="AE45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AF45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG45" s="3">
         <v>141200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>126000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>125300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>116400</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>125700</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>115400</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>136700</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>212700</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>120200</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>105800</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>95900</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4218,299 +4320,308 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>568800</v>
+        <v>190600</v>
       </c>
       <c r="E47" s="3">
-        <v>554500</v>
+        <v>187100</v>
       </c>
       <c r="F47" s="3">
-        <v>557500</v>
+        <v>191800</v>
       </c>
       <c r="G47" s="3">
-        <v>553700</v>
+        <v>194700</v>
       </c>
       <c r="H47" s="3">
-        <v>557400</v>
+        <v>192700</v>
       </c>
       <c r="I47" s="3">
-        <v>548500</v>
+        <v>196100</v>
       </c>
       <c r="J47" s="3">
+        <v>192100</v>
+      </c>
+      <c r="K47" s="3">
         <v>546400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>597900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>615300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>491000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>495800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>215800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>219200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>385000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>391600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>397600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>379700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>400100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>426800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>432600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>439400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>444900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>453800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>454700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>456200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>455800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>114400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>149800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>94200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>96500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>96000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>94500</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4581500</v>
+      </c>
+      <c r="E48" s="3">
         <v>4576900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4588700</v>
       </c>
-      <c r="F48" s="3">
-        <v>4617300</v>
-      </c>
       <c r="G48" s="3">
+        <v>4628900</v>
+      </c>
+      <c r="H48" s="3">
         <v>4603000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4751900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4797000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4959300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5018900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5045100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5156100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5162900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5228700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5269400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5279400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5285000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5306300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5358500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5363200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5350700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5354400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5388400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5447200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5853500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5975600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5993700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6108800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5994400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5972800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1995900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1993600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2009900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1999800</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E49" s="3">
         <v>27700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>28300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>30900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>32700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>36000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>39400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>40100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>48300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>49800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>52900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>54100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>76400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>79700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>81500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>82800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>85900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>93500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>96800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>101500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>105000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>108900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>119700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>131100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>142900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>156300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>161400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>167100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>262800</v>
-      </c>
-      <c r="AF49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG49" s="3" t="s">
         <v>8</v>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5900</v>
+        <v>103900</v>
       </c>
       <c r="E52" s="3">
-        <v>6000</v>
+        <v>108500</v>
       </c>
       <c r="F52" s="3">
-        <v>5400</v>
-      </c>
-      <c r="G52" s="3">
-        <v>5600</v>
+        <v>109900</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H52" s="3">
-        <v>5100</v>
+        <v>112900</v>
       </c>
       <c r="I52" s="3">
-        <v>5200</v>
+        <v>115500</v>
       </c>
       <c r="J52" s="3">
+        <v>112900</v>
+      </c>
+      <c r="K52" s="3">
         <v>4600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4900</v>
-      </c>
-      <c r="L52" s="3">
-        <v>4400</v>
       </c>
       <c r="M52" s="3">
         <v>4400</v>
       </c>
       <c r="N52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="O52" s="3">
         <v>3900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5100</v>
-      </c>
-      <c r="P52" s="3">
-        <v>4600</v>
       </c>
       <c r="Q52" s="3">
         <v>4600</v>
       </c>
       <c r="R52" s="3">
+        <v>4600</v>
+      </c>
+      <c r="S52" s="3">
         <v>6400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>10000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>9900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>280500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>103200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>186800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>11800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>68800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>12500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>11200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>9000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5366100</v>
+      </c>
+      <c r="E54" s="3">
         <v>5351100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5374400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5386200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5380600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5524300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5556300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5747700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5844900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5961400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5884900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5966700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6209500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5822100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5963800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5985600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5991600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6023600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6092300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6069300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6068000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6123200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6455100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6665300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6910300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7028100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6984600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7032300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6588300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2254000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2240100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2265900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2239400</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,132 +5230,136 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>83200</v>
+        <v>71300</v>
       </c>
       <c r="E57" s="3">
-        <v>79100</v>
+        <v>62500</v>
       </c>
       <c r="F57" s="3">
-        <v>120500</v>
+        <v>59000</v>
       </c>
       <c r="G57" s="3">
-        <v>106900</v>
+        <v>73800</v>
       </c>
       <c r="H57" s="3">
-        <v>105500</v>
+        <v>78300</v>
       </c>
       <c r="I57" s="3">
-        <v>121600</v>
+        <v>74700</v>
       </c>
       <c r="J57" s="3">
+        <v>94000</v>
+      </c>
+      <c r="K57" s="3">
         <v>124100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>123200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>101100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>92900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>121500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>108600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>103300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>105900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>130200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>125600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>143300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>112500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>98400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>92100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>90800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>72900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>94800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>86900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>105300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>102400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>102500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>116100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>37100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>33400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>39600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>1700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>97800</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5302,67 +5436,70 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>29600</v>
+        <v>19500</v>
       </c>
       <c r="E59" s="3">
-        <v>33700</v>
+        <v>20800</v>
       </c>
       <c r="F59" s="3">
-        <v>16500</v>
+        <v>20000</v>
       </c>
       <c r="G59" s="3">
-        <v>21100</v>
+        <v>39900</v>
       </c>
       <c r="H59" s="3">
-        <v>16400</v>
+        <v>28600</v>
       </c>
       <c r="I59" s="3">
-        <v>21400</v>
+        <v>30800</v>
       </c>
       <c r="J59" s="3">
+        <v>27600</v>
+      </c>
+      <c r="K59" s="3">
         <v>18200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>25400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>18100</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V59" s="3">
-        <v>9800</v>
+      <c r="V59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W59" s="3">
         <v>9800</v>
@@ -5371,16 +5508,16 @@
         <v>9800</v>
       </c>
       <c r="Y59" s="3">
+        <v>9800</v>
+      </c>
+      <c r="Z59" s="3">
         <v>10000</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB59" s="3">
-        <v>0</v>
+      <c r="AB59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC59" s="3">
         <v>0</v>
@@ -5403,31 +5540,34 @@
       <c r="AI59" s="3">
         <v>0</v>
       </c>
+      <c r="AJ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>115200</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>102200</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>102900</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>228000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>128500</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>122900</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>144500</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5504,132 +5644,138 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2446600</v>
+        <v>2477800</v>
       </c>
       <c r="E61" s="3">
-        <v>2463400</v>
+        <v>2457300</v>
       </c>
       <c r="F61" s="3">
-        <v>2414100</v>
+        <v>2473300</v>
       </c>
       <c r="G61" s="3">
-        <v>2349500</v>
+        <v>2328800</v>
       </c>
       <c r="H61" s="3">
-        <v>2420000</v>
+        <v>2349000</v>
       </c>
       <c r="I61" s="3">
-        <v>2396600</v>
+        <v>2419000</v>
       </c>
       <c r="J61" s="3">
+        <v>2395100</v>
+      </c>
+      <c r="K61" s="3">
         <v>2506800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2446900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2480200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2357500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2394500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2702100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2266300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2281600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2372400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2423000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2455300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2479300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2402100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2603100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2686000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3230200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3232000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3368600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3423800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3361100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3394500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3005500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1220100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1202400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1210700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1187400</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>28300</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>29700</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>31100</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>26800</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
+        <v>34200</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>38700</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>40500</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -5706,8 +5852,11 @@
       <c r="AI62" s="3">
         <v>0</v>
       </c>
+      <c r="AJ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2621300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2589100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2607300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2583600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2511700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2580600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2580100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2691300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2636200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2643700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2523400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2587200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2880400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2439100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2460400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2576400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2627300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2662300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2697100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2580800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2785600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2867100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3408700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3414900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3547400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3624600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3562400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3599500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3219200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1257300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1235800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1250300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1225600</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6430,7 +6598,7 @@
         <v>0</v>
       </c>
       <c r="AC70" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD70" s="3">
         <v>100</v>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>100</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>-1808200</v>
-      </c>
-      <c r="E72" s="3">
-        <v>-1762000</v>
-      </c>
-      <c r="F72" s="3">
-        <v>-1718300</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-1665000</v>
-      </c>
-      <c r="H72" s="3">
-        <v>-1579900</v>
-      </c>
-      <c r="I72" s="3">
-        <v>-1531200</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K72" s="3">
         <v>-1451900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-1296900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1177000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1124100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1095200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1001200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-944500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-746500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-716200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-689800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-663900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-631300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-573300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-523700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-460800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-462600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-271600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-171100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-125600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-238600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-217200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-225500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-214100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-203600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-192200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-185000</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2744800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2762000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2767200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2802500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2868900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2943700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2976200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3056400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3208700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3317700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3361500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3379500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3329100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3383100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3503400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3409200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3364300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3361300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3395200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3488500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3282400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3256100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3046500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3250400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3362900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3403500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3422100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3432700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3369000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>996600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1004300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1015500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1013800</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E81" s="3">
         <v>24000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>26300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>17200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-15100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>21200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-84900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-50100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>16800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>40600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-24400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-132600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>33400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>37100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>36500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>29600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>35200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>39700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>23300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>83700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-77700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-19400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>35200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>193600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>59900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>101400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>12500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>18000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>16300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>20600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,55 +7599,56 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>41700</v>
+        <v>43200</v>
       </c>
       <c r="E83" s="3">
-        <v>42900</v>
+        <v>44100</v>
       </c>
       <c r="F83" s="3">
-        <v>42900</v>
+        <v>52800</v>
       </c>
       <c r="G83" s="3">
-        <v>43200</v>
+        <v>32300</v>
       </c>
       <c r="H83" s="3">
-        <v>44100</v>
+        <v>47400</v>
       </c>
       <c r="I83" s="3">
-        <v>52800</v>
+        <v>45200</v>
       </c>
       <c r="J83" s="3">
+        <v>45300</v>
+      </c>
+      <c r="K83" s="3">
         <v>49900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>47400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>45200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>45300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>45100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>45000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>44500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>44400</v>
-      </c>
-      <c r="R83" s="3">
-        <v>44200</v>
       </c>
       <c r="S83" s="3">
         <v>44200</v>
@@ -7461,49 +7660,52 @@
         <v>44200</v>
       </c>
       <c r="V83" s="3">
+        <v>44200</v>
+      </c>
+      <c r="W83" s="3">
         <v>44000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>43100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>49500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>44900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>48100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>48500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>46800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>48000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>51000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>26600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>17200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>19100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>17200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>97700</v>
+      </c>
+      <c r="E89" s="3">
         <v>80100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>52800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>78700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>83200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>70300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>68300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>67600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>108500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>76600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>63100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>97900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>106200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>83700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>68500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>89400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>96900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>93800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>74800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>95500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>85100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>137900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>54000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>77600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>71500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>109900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>101600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>82500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>22700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>31600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>42900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>39300</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,70 +8365,71 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-36100</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-38900</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-39600</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3">
         <v>-8200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-63400</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3">
         <v>-20600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-37300</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-33500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-28700</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-25700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-67300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-36200</v>
-      </c>
-      <c r="W91" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>8</v>
@@ -8216,38 +8437,41 @@
       <c r="Y91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="Z91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-22500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-25000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-100</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-57000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-57300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-61800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>59900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>113200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-31200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-57000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-90900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-37200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-258800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-41900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-35400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-31600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-29100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-69800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-35700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-19300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>311500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>6300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>57800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-19400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>219500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-516400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>120600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-296800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-31200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-82500</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-69500</v>
+        <v>70300</v>
       </c>
       <c r="E96" s="3">
-        <v>-69400</v>
+        <v>69500</v>
       </c>
       <c r="F96" s="3">
-        <v>-69400</v>
+        <v>69400</v>
       </c>
       <c r="G96" s="3">
-        <v>-69400</v>
+        <v>69400</v>
       </c>
       <c r="H96" s="3">
-        <v>-69400</v>
+        <v>69400</v>
       </c>
       <c r="I96" s="3">
-        <v>-69400</v>
+        <v>69400</v>
       </c>
       <c r="J96" s="3">
-        <v>-69300</v>
+        <v>69400</v>
       </c>
       <c r="K96" s="3">
         <v>-69300</v>
@@ -8622,64 +8856,64 @@
         <v>-69300</v>
       </c>
       <c r="N96" s="3">
+        <v>-69300</v>
+      </c>
+      <c r="O96" s="3">
         <v>-68600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-66300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-64800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-63200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-62600</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-61700</v>
       </c>
       <c r="T96" s="3">
         <v>-61700</v>
       </c>
       <c r="U96" s="3">
+        <v>-61700</v>
+      </c>
+      <c r="V96" s="3">
         <v>-92400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-88200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-85500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-81500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-80300</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-80200</v>
       </c>
       <c r="AA96" s="3">
         <v>-80200</v>
       </c>
       <c r="AB96" s="3">
+        <v>-80200</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-81900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-82800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-95300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-26100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-30700</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-30000</v>
       </c>
       <c r="AH96" s="3">
         <v>-30000</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>-30000</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>-30000</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-46400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-20200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-9400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-136400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-68500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-196100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-13500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-91600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>56000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-112500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-274600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>371600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-69300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-60100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-60400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-90500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>8900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-50400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-83500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-424800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-87500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-212800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-138400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-161800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-114400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>341000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>317900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-16700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-43300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>300</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-300</v>
-      </c>
       <c r="H101" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="I101" s="3">
-        <v>-600</v>
+        <v>600</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>-100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>600</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-100</v>
-      </c>
-      <c r="P101" s="3">
-        <v>100</v>
       </c>
       <c r="Q101" s="3">
         <v>100</v>
       </c>
       <c r="R101" s="3">
+        <v>100</v>
+      </c>
+      <c r="S101" s="3">
         <v>300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-200</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>100</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-23600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>19200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>22800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-40400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>42200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-86600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-435500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>477500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>44400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-36000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>23700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-25600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>13300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>9500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-17800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>24800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-27000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-79900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-86100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>167500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-529300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>544100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>20700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-12700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>6000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-84200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBRA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBRA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
   <si>
     <t>SBRA</t>
   </si>
@@ -656,467 +656,479 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>183000</v>
+      </c>
+      <c r="E8" s="3">
         <v>178200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>176200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>166200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>162600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>161000</v>
-      </c>
-      <c r="I8" s="3">
-        <v>160500</v>
       </c>
       <c r="J8" s="3">
         <v>160500</v>
       </c>
       <c r="K8" s="3">
+        <v>160500</v>
+      </c>
+      <c r="L8" s="3">
         <v>165000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>140800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>156000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>163100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>135700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>128600</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>152400</v>
       </c>
       <c r="R8" s="3">
         <v>152400</v>
       </c>
       <c r="S8" s="3">
+        <v>152400</v>
+      </c>
+      <c r="T8" s="3">
         <v>151500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>142100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>153900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>149300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>155800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>149800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>152500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>136800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>139200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>151800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>166300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>166100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>166500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>111800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>64700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>62700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>61800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>61900</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E9" s="3">
         <v>58400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>54600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>53900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>49500</v>
-      </c>
-      <c r="H9" s="3">
-        <v>49200</v>
       </c>
       <c r="I9" s="3">
         <v>49200</v>
       </c>
       <c r="J9" s="3">
+        <v>49200</v>
+      </c>
+      <c r="K9" s="3">
         <v>47600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>39200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>36700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>34000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>33100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>30900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>30000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>28500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>28000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>26900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>26500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>26300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>27000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>26000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>24000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>24200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>12000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>12500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>12600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>12300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>12100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2400</v>
-      </c>
-      <c r="AI9" s="3">
-        <v>1400</v>
       </c>
       <c r="AJ9" s="3">
         <v>1400</v>
       </c>
+      <c r="AK9" s="3">
+        <v>1400</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>123200</v>
+      </c>
+      <c r="E10" s="3">
         <v>119900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>121600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>112300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>113100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>111800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>111300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>112900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>125800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>104100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>122000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>130000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>104800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>98600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>123900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>124400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>124600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>115600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>127600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>122300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>129800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>125800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>128300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>124800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>126700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>139200</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>154000</v>
       </c>
       <c r="AD10" s="3">
         <v>154000</v>
       </c>
       <c r="AE10" s="3">
+        <v>154000</v>
+      </c>
+      <c r="AF10" s="3">
         <v>160600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>106700</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>60300</v>
       </c>
       <c r="AH10" s="3">
         <v>60300</v>
       </c>
       <c r="AI10" s="3">
+        <v>60300</v>
+      </c>
+      <c r="AJ10" s="3">
         <v>60400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,101 +1377,104 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-6800</v>
+      </c>
+      <c r="E14" s="3">
         <v>5700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>13600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>8000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>42300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>29800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>21200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>61000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>11700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-2000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>43400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2200</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>1700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>6000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>8300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>14600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-45100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>103100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>2900</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>600</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
@@ -1465,58 +1484,61 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E15" s="3">
         <v>42700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>41700</v>
-      </c>
-      <c r="F15" s="3">
-        <v>42900</v>
       </c>
       <c r="G15" s="3">
         <v>42900</v>
       </c>
       <c r="H15" s="3">
+        <v>42900</v>
+      </c>
+      <c r="I15" s="3">
         <v>43200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>44100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>52800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>49900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>47400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>45200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>45300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>45100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>45000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>44500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>44400</v>
-      </c>
-      <c r="S15" s="3">
-        <v>44200</v>
       </c>
       <c r="T15" s="3">
         <v>44200</v>
@@ -1528,49 +1550,52 @@
         <v>44200</v>
       </c>
       <c r="W15" s="3">
+        <v>44200</v>
+      </c>
+      <c r="X15" s="3">
         <v>44000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>43100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>49500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>44900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>48100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>48500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>46800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>48000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>51600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>25900</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>17200</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>19100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>17200</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>115100</v>
+      </c>
+      <c r="E17" s="3">
         <v>113500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>109000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>108700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>109100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>103200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>102800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>110900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>153900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>186800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>129700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>117200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>160300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>115200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>110900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>114700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>111800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>114000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>112000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>111500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>116500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>125300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>67000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>211100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>141700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>115500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>105500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>105900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>109500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>97500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>49000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>45800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>40800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E18" s="3">
         <v>64700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>67200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>57500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>53600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>57800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>57700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>49600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-46000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>26300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>45900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-24600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>41500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>37700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>39700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>28100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>41900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>37800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>39300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>24500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>85500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-74300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>36300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>60800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>60200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>57000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>14300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>15700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>16900</v>
-      </c>
-      <c r="AI18" s="3">
-        <v>21000</v>
       </c>
       <c r="AJ18" s="3">
         <v>21000</v>
       </c>
+      <c r="AK18" s="3">
+        <v>21000</v>
+      </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,243 +1882,250 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>2000</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>-96000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-9200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-5000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-173500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>8200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-11900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-15700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>140600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>47400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>5000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>110200</v>
+      </c>
+      <c r="E21" s="3">
         <v>107500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>109000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>100300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>96500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>99100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>101800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>102400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-34900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-2100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>62200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>86100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>21300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>55400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-87600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>78500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>80600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>80500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>74300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>80400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>84900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>67200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>134000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-32100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>29900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>84400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>248200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>111000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>155400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>41400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>37900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>38100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>40600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E22" s="3">
         <v>29500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>29300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>28400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>27900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>28200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>28300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>28500</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -2162,123 +2201,129 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E23" s="3">
         <v>29500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>24400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>26700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>17600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-14600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>21500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-84800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-49500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>17100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>40900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-23800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>10300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-132100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>34100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>36500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>36300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>30100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>36300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>40900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>24100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>84500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-77100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-18200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>36000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>201400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>63000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>104500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>14900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>20700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>19000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>23400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>400</v>
+      </c>
+      <c r="E24" s="3">
         <v>-300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>400</v>
-      </c>
-      <c r="F24" s="3">
-        <v>500</v>
       </c>
       <c r="G24" s="3">
         <v>500</v>
@@ -2287,91 +2332,94 @@
         <v>500</v>
       </c>
       <c r="I24" s="3">
+        <v>500</v>
+      </c>
+      <c r="J24" s="3">
         <v>300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>600</v>
-      </c>
-      <c r="M24" s="3">
-        <v>300</v>
       </c>
       <c r="N24" s="3">
         <v>300</v>
       </c>
       <c r="O24" s="3">
+        <v>300</v>
+      </c>
+      <c r="P24" s="3">
         <v>500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>600</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>500</v>
       </c>
       <c r="AE24" s="3">
         <v>500</v>
       </c>
       <c r="AF24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AG24" s="3">
         <v>-200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E26" s="3">
         <v>29800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>24000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>26300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>17200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-15100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>21200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-9500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-84900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-50100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>40600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-24400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-132600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>33400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>37100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>36500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>29600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>35200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>39700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>23300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>83700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-77700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-19400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>35200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>200800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>62500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>104000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>15100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>20500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>18800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>23200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E27" s="3">
         <v>29800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>24000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>26300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>17200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-15100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>21200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-9500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-84900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-50100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>40600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-24400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-132600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>33400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>37100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>36500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>29600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>35200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>39700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>23300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>83700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-77700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-19400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>35200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>193600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>59900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>101400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>12500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>18000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>16300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>20600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,216 +3164,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-2000</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>96000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>9200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>5000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>173500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-8200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>11900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>15700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-140600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-47400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E33" s="3">
         <v>29800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>24000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>26300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>17200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-15100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>21200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-9500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-84900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-50100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>40600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-24400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-132600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>33400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>37100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>36500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>29600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>35200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>39700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>23300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>83700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-77700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-19400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>35200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>193600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>59900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>101400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>12500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>18000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>16300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>20600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E35" s="3">
         <v>29800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>24000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>26300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>17200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-15100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>21200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-9500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-84900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-50100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>40600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-24400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-132600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>33400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>37100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>36500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>29600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>35200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>39700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>23300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>83700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-77700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-19400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>35200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>193600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>59900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>101400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>12500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>18000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>16300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>20600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,139 +3784,143 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>60500</v>
+      </c>
+      <c r="E41" s="3">
         <v>63000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>36400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>59900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>41300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>33300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>27200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>33500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>49300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>26300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>67200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>24800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>112000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>546300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>69300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>24900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>59100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>35000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>28300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>54100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>39100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>29400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>47600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>22900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>50200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>36300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>38800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>46400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>518600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>30900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>13200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>12800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>25700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>21500</v>
+      </c>
+      <c r="E42" s="3">
         <v>10300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>27000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>27100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>18900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>39300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>31100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>19800</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3907,35 +3996,38 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>149100</v>
+      </c>
+      <c r="E43" s="3">
         <v>46400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>46100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>43700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>147100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>42000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>42300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>37400</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -4011,8 +4103,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,8 +4132,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4115,8 +4210,11 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4141,8 +4239,8 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -4201,53 +4299,56 @@
       <c r="AD45" s="3">
         <v>0</v>
       </c>
-      <c r="AE45" s="3" t="s">
-        <v>8</v>
+      <c r="AE45" s="3">
+        <v>0</v>
       </c>
       <c r="AF45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AG45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH45" s="3">
         <v>141200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>126000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>125300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>116400</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>237000</v>
+      </c>
+      <c r="E46" s="3">
         <v>125700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>115400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>136700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>212700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>120200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>105800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>95900</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4323,308 +4424,317 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>182900</v>
+      </c>
+      <c r="E47" s="3">
         <v>190600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>187100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>191800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>194700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>192700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>196100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>192100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>546400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>597900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>615300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>491000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>495800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>215800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>219200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>385000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>391600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>397600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>379700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>400100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>426800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>432600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>439400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>444900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>453800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>454700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>456200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>455800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>114400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>149800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>94200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>96500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>96000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>94500</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4520700</v>
+      </c>
+      <c r="E48" s="3">
         <v>4581500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4576900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4588700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4628900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4603000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4751900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4797000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4959300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5018900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5045100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5156100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5162900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5228700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5269400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5279400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5285000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5306300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5358500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5363200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5350700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5354400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5388400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5447200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5853500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5975600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5993700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6108800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5994400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5972800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1995900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1993600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2009900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1999800</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E49" s="3">
         <v>28800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>27700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>28300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>30900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>32700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>36000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>39400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>40100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>48300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>49800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>52900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>54100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>76400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>79700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>81500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>82800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>85900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>93500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>96800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>101500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>105000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>108900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>119700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>131100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>142900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>156300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>161400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>167100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>262800</v>
-      </c>
-      <c r="AG49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH49" s="3" t="s">
         <v>8</v>
@@ -4635,8 +4745,11 @@
       <c r="AJ49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,112 +4959,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3">
         <v>103900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>108500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>109900</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="H52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>112900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>115500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>112900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4900</v>
-      </c>
-      <c r="M52" s="3">
-        <v>4400</v>
       </c>
       <c r="N52" s="3">
         <v>4400</v>
       </c>
       <c r="O52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="P52" s="3">
         <v>3900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5100</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>4600</v>
       </c>
       <c r="R52" s="3">
         <v>4600</v>
       </c>
       <c r="S52" s="3">
+        <v>4600</v>
+      </c>
+      <c r="T52" s="3">
         <v>6400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>10000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>10200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>9900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>280500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>103200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>186800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>11800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>68800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>12500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>9400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>11200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5303700</v>
+      </c>
+      <c r="E54" s="3">
         <v>5366100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5351100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5374400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5386200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5380600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5524300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5556300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5747700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5844900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5961400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5884900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5966700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6209500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5822100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5963800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5985600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5991600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6023600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6092300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6069300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6068000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6123200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6455100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6665300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6910300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7028100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6984600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7032300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6588300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2254000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2240100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2265900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>2239400</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,139 +5360,143 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E57" s="3">
         <v>71300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>62500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>59000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>73800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>78300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>74700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>94000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>124100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>123200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>101100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>92900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>121500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>108600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>103300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>105900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>130200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>125600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>143300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>112500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>98400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>92100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>90800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>72900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>94800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>86900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>105300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>102400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>102500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>116100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>37100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>33400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>39600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E58" s="3">
         <v>1100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2500</v>
       </c>
-      <c r="G58" s="3">
-        <v>97800</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1500</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5439,70 +5572,73 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E59" s="3">
         <v>19500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20000</v>
       </c>
-      <c r="G59" s="3">
-        <v>39900</v>
-      </c>
       <c r="H59" s="3">
+        <v>34200</v>
+      </c>
+      <c r="I59" s="3">
         <v>28600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>30800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>27600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>22000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>25400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>16100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>18100</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W59" s="3">
-        <v>9800</v>
+      <c r="W59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X59" s="3">
         <v>9800</v>
@@ -5511,16 +5647,16 @@
         <v>9800</v>
       </c>
       <c r="Z59" s="3">
+        <v>9800</v>
+      </c>
+      <c r="AA59" s="3">
         <v>10000</v>
-      </c>
-      <c r="AA59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC59" s="3">
-        <v>0</v>
+      <c r="AC59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD59" s="3">
         <v>0</v>
@@ -5543,35 +5679,38 @@
       <c r="AJ59" s="3">
         <v>0</v>
       </c>
+      <c r="AK59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>118300</v>
+      </c>
+      <c r="E60" s="3">
         <v>115200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>102200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>102900</v>
       </c>
-      <c r="G60" s="3">
-        <v>228000</v>
-      </c>
       <c r="H60" s="3">
+        <v>124500</v>
+      </c>
+      <c r="I60" s="3">
         <v>128500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>122900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>144500</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5647,139 +5786,145 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2422300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2477800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2457300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2473300</v>
       </c>
-      <c r="G61" s="3">
-        <v>2328800</v>
-      </c>
       <c r="H61" s="3">
+        <v>2426600</v>
+      </c>
+      <c r="I61" s="3">
         <v>2349000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2419000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2395100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2506800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2446900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2480200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2357500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2394500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2702100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2266300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2281600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2372400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2423000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2455300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2479300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2402100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2603100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2686000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3230200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3232000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3368600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3423800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3361100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3394500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3005500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1220100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1202400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1210700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1187400</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E62" s="3">
         <v>28300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>29700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>31100</v>
       </c>
-      <c r="G62" s="3">
-        <v>26800</v>
-      </c>
       <c r="H62" s="3">
+        <v>32500</v>
+      </c>
+      <c r="I62" s="3">
         <v>34200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>38700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>40500</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
@@ -5855,8 +6000,11 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2562400</v>
+      </c>
+      <c r="E66" s="3">
         <v>2621300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2589100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2607300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2583600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2511700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2580600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2580100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2691300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2636200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2643700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2523400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2587200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2880400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2439100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2460400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2576400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2627300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2662300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2697100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2580800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2785600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2867100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3408700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3414900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3547400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3624600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3562400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3599500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3219200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1257300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1235800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1250300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1225600</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6601,7 +6768,7 @@
         <v>0</v>
       </c>
       <c r="AD70" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE70" s="3">
         <v>100</v>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>100</v>
       </c>
+      <c r="AK70" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,8 +6895,11 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6751,86 +6924,89 @@
       <c r="J72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="3">
         <v>-1451900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-1296900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1177000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1124100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1095200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1001200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-944500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-746500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-716200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-689800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-663900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-631300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-573300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-523700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-460800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-462600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-271600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-171100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-125600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-238600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-217200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-225500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-214100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-203600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-192200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-185000</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2741300</v>
+      </c>
+      <c r="E76" s="3">
         <v>2744800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2762000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2767200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2802500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2868900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2943700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2976200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3056400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3208700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3317700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3361500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3379500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3329100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3383100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3503400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3409200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3364300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3361300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3395200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3488500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3282400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3256100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3046500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3250400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3362900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3403500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3422100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3432700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3369000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>996600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1004300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1015500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1013800</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E81" s="3">
         <v>29800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>24000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>26300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>17200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-15100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>21200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-9500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-84900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-50100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>40600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-24400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-132600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>33400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>37100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>36500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>29600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>35200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>39700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>23300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>83700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-77700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-19400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>35200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>193600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>59900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>101400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>12500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>18000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>16300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>20600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,58 +7797,59 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>31300</v>
+      </c>
+      <c r="E83" s="3">
         <v>43200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>44100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>52800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>32300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>47400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>45200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>45300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>49900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>47400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>45200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>45300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>45100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>45000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>44500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>44400</v>
-      </c>
-      <c r="S83" s="3">
-        <v>44200</v>
       </c>
       <c r="T83" s="3">
         <v>44200</v>
@@ -7663,49 +7861,52 @@
         <v>44200</v>
       </c>
       <c r="W83" s="3">
+        <v>44200</v>
+      </c>
+      <c r="X83" s="3">
         <v>44000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>43100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>49500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>44900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>48100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>48500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>46800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>48000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>51000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>26600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>17200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>19100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>17200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E89" s="3">
         <v>97700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>80100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>52800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>78700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>83200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>70300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>68300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>67600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>108500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>76600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>63100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>97900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>106200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>83700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>68500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>89400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>96900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>93800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>74800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>95500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>85100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>137900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>54000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>77600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>71500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>109900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>101600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>82500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>22700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>31600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>42900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>39300</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,8 +8585,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8392,47 +8612,47 @@
       <c r="J91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K91" s="3">
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3">
         <v>-8200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-63400</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
         <v>-20600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-37300</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-33500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-28700</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-25700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-67300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-36200</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>8</v>
@@ -8440,38 +8660,41 @@
       <c r="Z91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AA91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-22500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-25000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-57000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-57300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-61800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>59900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>113200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-31200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-57000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-90900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-37200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-258800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-41900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-35400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-31600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-29100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-69800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-35700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-19300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>311500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>6300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>57800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-19400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>219500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-516400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>120600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-296800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-5400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-31200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-82500</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,19 +9052,20 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>71000</v>
+      </c>
+      <c r="E96" s="3">
         <v>70300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>69500</v>
-      </c>
-      <c r="F96" s="3">
-        <v>69400</v>
       </c>
       <c r="G96" s="3">
         <v>69400</v>
@@ -8847,7 +9080,7 @@
         <v>69400</v>
       </c>
       <c r="K96" s="3">
-        <v>-69300</v>
+        <v>69400</v>
       </c>
       <c r="L96" s="3">
         <v>-69300</v>
@@ -8859,64 +9092,64 @@
         <v>-69300</v>
       </c>
       <c r="O96" s="3">
+        <v>-69300</v>
+      </c>
+      <c r="P96" s="3">
         <v>-68600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-66300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-64800</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-63200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-62600</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-61700</v>
       </c>
       <c r="U96" s="3">
         <v>-61700</v>
       </c>
       <c r="V96" s="3">
+        <v>-61700</v>
+      </c>
+      <c r="W96" s="3">
         <v>-92400</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-88200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-85500</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-81500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-80300</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-80200</v>
       </c>
       <c r="AB96" s="3">
         <v>-80200</v>
       </c>
       <c r="AC96" s="3">
+        <v>-80200</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-81900</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-82800</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-95300</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-26100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-30700</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-30000</v>
       </c>
       <c r="AI96" s="3">
         <v>-30000</v>
@@ -8924,8 +9157,11 @@
       <c r="AJ96" s="3">
         <v>-30000</v>
       </c>
+      <c r="AK96" s="3">
+        <v>-30000</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-101000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-14000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-46400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-20200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-136400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-68500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-196100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-13500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-91600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>56000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-112500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-274600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>371600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-69300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-60100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-60400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-90500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>8900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-50400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-83500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-424800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-87500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-212800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-138400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-161800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-114400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>341000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>317900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-16700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-43300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-5000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-300</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>600</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
         <v>0</v>
       </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>100</v>
       </c>
       <c r="R101" s="3">
         <v>100</v>
       </c>
       <c r="S101" s="3">
+        <v>100</v>
+      </c>
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-200</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>100</v>
       </c>
-      <c r="AH101" s="3">
-        <v>0</v>
-      </c>
       <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ101" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E102" s="3">
         <v>26700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-23600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>19200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>22800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-40400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>42200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-86600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-435500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>477500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>44400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-36000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>23700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>5000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-25600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>13300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>9500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-17800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>24800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-27000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-79900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-86100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>167500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-529300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>544100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>20700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-12700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-84200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBRA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBRA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
   <si>
     <t>SBRA</t>
   </si>
@@ -656,479 +656,492 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>183800</v>
+      </c>
+      <c r="E8" s="3">
         <v>183000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>178200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>176200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>166200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>162600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>161000</v>
-      </c>
-      <c r="J8" s="3">
-        <v>160500</v>
       </c>
       <c r="K8" s="3">
         <v>160500</v>
       </c>
       <c r="L8" s="3">
+        <v>160500</v>
+      </c>
+      <c r="M8" s="3">
         <v>165000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>140800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>156000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>163100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>135700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>128600</v>
-      </c>
-      <c r="R8" s="3">
-        <v>152400</v>
       </c>
       <c r="S8" s="3">
         <v>152400</v>
       </c>
       <c r="T8" s="3">
+        <v>152400</v>
+      </c>
+      <c r="U8" s="3">
         <v>151500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>142100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>153900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>149300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>155800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>149800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>152500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>136800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>139200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>151800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>166300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>166100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>166500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>111800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>64700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>62700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>61800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>61900</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E9" s="3">
         <v>59700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>58400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>54600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>53900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>49500</v>
-      </c>
-      <c r="I9" s="3">
-        <v>49200</v>
       </c>
       <c r="J9" s="3">
         <v>49200</v>
       </c>
       <c r="K9" s="3">
+        <v>49200</v>
+      </c>
+      <c r="L9" s="3">
         <v>47600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>39200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>36700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>34000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>33100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>30900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>30000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>28500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>28000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>26900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>26500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>26300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>27000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>26000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>24000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>24200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>12000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>12500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>12600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>12300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>12100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2400</v>
-      </c>
-      <c r="AJ9" s="3">
-        <v>1400</v>
       </c>
       <c r="AK9" s="3">
         <v>1400</v>
       </c>
+      <c r="AL9" s="3">
+        <v>1400</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>124000</v>
+      </c>
+      <c r="E10" s="3">
         <v>123200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>119900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>121600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>112300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>113100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>111800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>111300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>112900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>125800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>104100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>122000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>130000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>104800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>98600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>123900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>124400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>124600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>115600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>127600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>122300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>129800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>125800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>128300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>124800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>126700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>139200</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>154000</v>
       </c>
       <c r="AE10" s="3">
         <v>154000</v>
       </c>
       <c r="AF10" s="3">
+        <v>154000</v>
+      </c>
+      <c r="AG10" s="3">
         <v>160600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>106700</v>
-      </c>
-      <c r="AH10" s="3">
-        <v>60300</v>
       </c>
       <c r="AI10" s="3">
         <v>60300</v>
       </c>
       <c r="AJ10" s="3">
+        <v>60300</v>
+      </c>
+      <c r="AK10" s="3">
         <v>60400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,104 +1397,107 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>-6800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>13600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>8000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>42300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>29800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>21200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>61000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>11700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-2000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>43400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2200</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>1700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>6000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>8300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>14600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-45100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>103100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>2900</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>500</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>600</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
@@ -1487,61 +1507,64 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E15" s="3">
         <v>42300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>42700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>41700</v>
-      </c>
-      <c r="G15" s="3">
-        <v>42900</v>
       </c>
       <c r="H15" s="3">
         <v>42900</v>
       </c>
       <c r="I15" s="3">
+        <v>42900</v>
+      </c>
+      <c r="J15" s="3">
         <v>43200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>44100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>52800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>49900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>47400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>45200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>45300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>45100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>45000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>44500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>44400</v>
-      </c>
-      <c r="T15" s="3">
-        <v>44200</v>
       </c>
       <c r="U15" s="3">
         <v>44200</v>
@@ -1553,49 +1576,52 @@
         <v>44200</v>
       </c>
       <c r="X15" s="3">
+        <v>44200</v>
+      </c>
+      <c r="Y15" s="3">
         <v>44000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>43100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>49500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>44900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>48100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>48500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>46800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>48000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>51600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>25900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>17200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>19100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>17200</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E17" s="3">
         <v>115100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>113500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>109000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>108700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>109100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>103200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>102800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>110900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>153900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>186800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>129700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>117200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>160300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>115200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>110900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>114700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>111800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>114000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>112000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>111500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>116500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>125300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>67000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>211100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>141700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>115500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>105500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>105900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>109500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>97500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>49000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>45800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>40800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>67800</v>
+      </c>
+      <c r="E18" s="3">
         <v>67900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>64700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>67200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>57500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>53600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>57800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>57700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>49600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-46000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>26300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>45900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>41500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>37700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>39700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>28100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>41900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>37800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>39300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>24500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>85500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-74300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>36300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>60800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>60200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>57000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>14300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>15700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>16900</v>
-      </c>
-      <c r="AJ18" s="3">
-        <v>21000</v>
       </c>
       <c r="AK18" s="3">
         <v>21000</v>
       </c>
+      <c r="AL18" s="3">
+        <v>21000</v>
+      </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,252 +1916,259 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>2000</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>-96000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-9200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-173500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>8200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-11900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-15700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>140600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>47400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>5000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>2400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>111300</v>
+      </c>
+      <c r="E21" s="3">
         <v>110200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>107500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>109000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>100300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>96500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>99100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>101800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>102400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-34900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-2100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>62200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>86100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>21300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>55400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-87600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>78500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>80600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>80500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>74300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>80400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>84900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>67200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>134000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-32100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>29900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>84400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>248200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>111000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>155400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>41400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>37900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>38100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>40600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E22" s="3">
         <v>27600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>29500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>29300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>28400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>27900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>28200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>28300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>28500</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -2204,115 +2244,121 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>40700</v>
+      </c>
+      <c r="E23" s="3">
         <v>47100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>29500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>24400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>26700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>17600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>21500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-84800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-49500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>17100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>40900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-23800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>10300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-132100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>34100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>36500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>36300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>30100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>36300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>40900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>24100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>84500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-77100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-18200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>36000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>201400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>63000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>104500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>14900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>20700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>19000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>23400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2320,13 +2366,13 @@
         <v>400</v>
       </c>
       <c r="E24" s="3">
+        <v>400</v>
+      </c>
+      <c r="F24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>400</v>
-      </c>
-      <c r="G24" s="3">
-        <v>500</v>
       </c>
       <c r="H24" s="3">
         <v>500</v>
@@ -2335,91 +2381,94 @@
         <v>500</v>
       </c>
       <c r="J24" s="3">
+        <v>500</v>
+      </c>
+      <c r="K24" s="3">
         <v>300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>600</v>
-      </c>
-      <c r="N24" s="3">
-        <v>300</v>
       </c>
       <c r="O24" s="3">
         <v>300</v>
       </c>
       <c r="P24" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q24" s="3">
         <v>500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>600</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>500</v>
       </c>
       <c r="AF24" s="3">
         <v>500</v>
       </c>
       <c r="AG24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH24" s="3">
         <v>-200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E26" s="3">
         <v>46700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>29800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>24000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>26300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>17200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-15100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>21200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-84900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-50100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>16800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>40600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>10200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-132600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>33400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>37100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>36500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>29600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>35200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>39700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>23300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>83700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-77700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-19400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>35200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>200800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>62500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>104000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>15100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>20500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>18800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>23200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E27" s="3">
         <v>46700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>29800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>24000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>26300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>17200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-15100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>21200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-84900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-50100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>16800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>40600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>10200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-132600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>33400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>37100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>36500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>29600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>35200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>39700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>23300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>83700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-77700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-19400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>35200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>193600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>59900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>101400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>12500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>18000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>16300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>20600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,222 +3234,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
         <v>0</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-2000</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>96000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>9200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>173500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-8200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>11900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>15700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-140600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-47400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E33" s="3">
         <v>46700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>29800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>24000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>26300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>17200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-15100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>21200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-84900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-50100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>40600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>10200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-132600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>33400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>37100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>36500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>29600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>35200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>39700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>23300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>83700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-77700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-19400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>35200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>193600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>59900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>101400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>12500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>18000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>16300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>20600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E35" s="3">
         <v>46700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>29800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>24000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>26300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>17200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-15100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>21200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-84900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-50100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>40600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>10200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-132600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>33400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>37100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>36500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>29600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>35200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>39700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>23300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>83700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-77700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-19400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>35200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>193600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>59900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>101400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>12500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>18000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>16300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>20600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,145 +3871,149 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E41" s="3">
         <v>60500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>63000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>59900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>41300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>33300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>27200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>33500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>49300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>26300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>67200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>24800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>112000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>546300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>69300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>24900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>59100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>35000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>28300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>54100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>39100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>29400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>47600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>22900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>50200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>36300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>38800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>46400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>518600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>30900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>13200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>12800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>25700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E42" s="3">
         <v>21500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>10300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>27000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>27100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>18900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>39300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>31100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>19800</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3999,38 +4089,41 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>46600</v>
+      </c>
+      <c r="E43" s="3">
         <v>149100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>46400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>46100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>43700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>147100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>42000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>42300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>37400</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -4106,8 +4199,11 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4135,8 +4231,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4213,8 +4309,11 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4242,8 +4341,8 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -4302,56 +4401,59 @@
       <c r="AE45" s="3">
         <v>0</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>8</v>
+      <c r="AF45" s="3">
+        <v>0</v>
       </c>
       <c r="AG45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AH45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI45" s="3">
         <v>141200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>126000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>125300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>116400</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E46" s="3">
         <v>237000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>125700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>115400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>136700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>212700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>120200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>105800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>95900</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4427,317 +4529,326 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>182800</v>
+      </c>
+      <c r="E47" s="3">
         <v>182900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>190600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>187100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>191800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>194700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>192700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>196100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>192100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>546400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>597900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>615300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>491000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>495800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>215800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>219200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>385000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>391600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>397600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>379700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>400100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>426800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>432600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>439400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>444900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>453800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>454700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>456200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>455800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>114400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>149800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>94200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>96500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>96000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>94500</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4495000</v>
+      </c>
+      <c r="E48" s="3">
         <v>4520700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4581500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4576900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4588700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4628900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4603000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4751900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4797000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4959300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5018900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5045100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5156100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5162900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5228700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5269400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5279400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5285000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5306300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5358500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5363200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5350700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5354400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5388400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5447200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5853500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5975600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5993700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6108800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5994400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5972800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1995900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1993600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2009900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1999800</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E49" s="3">
         <v>27500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>28800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>27700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>28300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>30900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>32700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>36000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>39400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>40100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>48300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>49800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>52900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>54100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>76400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>79700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>81500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>82800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>85900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>93500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>96800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>101500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>105000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>108900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>119700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>131100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>142900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>156300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>161400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>167100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>262800</v>
-      </c>
-      <c r="AH49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI49" s="3" t="s">
         <v>8</v>
@@ -4748,8 +4859,11 @@
       <c r="AK49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,115 +5079,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="D52" s="3">
+        <v>104200</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>103900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>108500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>109900</v>
       </c>
-      <c r="H52" s="3" t="s">
+      <c r="I52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>112900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>115500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>112900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4900</v>
-      </c>
-      <c r="N52" s="3">
-        <v>4400</v>
       </c>
       <c r="O52" s="3">
         <v>4400</v>
       </c>
       <c r="P52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="Q52" s="3">
         <v>3900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5100</v>
-      </c>
-      <c r="R52" s="3">
-        <v>4600</v>
       </c>
       <c r="S52" s="3">
         <v>4600</v>
       </c>
       <c r="T52" s="3">
+        <v>4600</v>
+      </c>
+      <c r="U52" s="3">
         <v>6400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>8400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>10000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>10200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>9900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>280500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>9400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>103200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>186800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>11800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>68800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>12500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>9400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>11200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>9000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5233200</v>
+      </c>
+      <c r="E54" s="3">
         <v>5303700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5366100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5351100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5374400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5386200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5380600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5524300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5556300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5747700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5844900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5961400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5884900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5966700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6209500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5822100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5963800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5985600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5991600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6023600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6092300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6069300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6068000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6123200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6455100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6665300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6910300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7028100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6984600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7032300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6588300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2254000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2240100</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>2265900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>2239400</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,145 +5491,149 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>61800</v>
+      </c>
+      <c r="E57" s="3">
         <v>67800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>71300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>62500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>59000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>73800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>78300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>74700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>94000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>124100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>123200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>101100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>92900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>121500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>108600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>103300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>105900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>130200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>125600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>143300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>112500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>98400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>92100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>90800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>72900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>94800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>86900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>105300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>102400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>102500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>116100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>37100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>33400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>39600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E58" s="3">
         <v>3600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2500</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1500</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5575,73 +5709,76 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E59" s="3">
         <v>30800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>19500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>20000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>34200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>28600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>30800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>27600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>22000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>16600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>25400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>21500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>17600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>16100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>18100</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X59" s="3">
-        <v>9800</v>
+      <c r="X59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y59" s="3">
         <v>9800</v>
@@ -5650,16 +5787,16 @@
         <v>9800</v>
       </c>
       <c r="AA59" s="3">
+        <v>9800</v>
+      </c>
+      <c r="AB59" s="3">
         <v>10000</v>
-      </c>
-      <c r="AB59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD59" s="3">
-        <v>0</v>
+      <c r="AD59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE59" s="3">
         <v>0</v>
@@ -5682,38 +5819,41 @@
       <c r="AK59" s="3">
         <v>0</v>
       </c>
+      <c r="AL59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>106700</v>
+      </c>
+      <c r="E60" s="3">
         <v>118300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>115200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>102200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>102900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>124500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>128500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>122900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>144500</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5789,145 +5929,151 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2399200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2422300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2477800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2457300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2473300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2426600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2349000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2419000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2395100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2506800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2446900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2480200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2357500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2394500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2702100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2266300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2281600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2372400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2423000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2455300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2479300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2402100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2603100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2686000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>3230200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3232000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3368600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3423800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3361100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3394500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3005500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1220100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1202400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1210700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1187400</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E62" s="3">
         <v>21700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>28300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>29700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>31100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>32500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>34200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>38700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>40500</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
@@ -6003,8 +6149,11 @@
       <c r="AK62" s="3">
         <v>0</v>
       </c>
+      <c r="AL62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2531000</v>
+      </c>
+      <c r="E66" s="3">
         <v>2562400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2621300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2589100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2607300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2583600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2511700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2580600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2580100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2691300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2636200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2643700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2523400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2587200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2880400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2439100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2460400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2576400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2627300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2662300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2697100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2580800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2785600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2867100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3408700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3414900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3547400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3624600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3562400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3599500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3219200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1257300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1235800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1250300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1225600</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6771,7 +6939,7 @@
         <v>0</v>
       </c>
       <c r="AE70" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF70" s="3">
         <v>100</v>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>100</v>
       </c>
+      <c r="AL70" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,8 +7069,11 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6927,86 +7101,89 @@
       <c r="K72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M72" s="3">
         <v>-1451900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-1296900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1177000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1124100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1095200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1001200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-944500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-746500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-716200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-689800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-663900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-631300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-573300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-523700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-460800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-462600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-271600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-171100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-125600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-238600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-217200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-225500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-214100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-203600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-192200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-185000</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2702200</v>
+      </c>
+      <c r="E76" s="3">
         <v>2741300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2744800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2762000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2767200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2802500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2868900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2943700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2976200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3056400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3208700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3317700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3361500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3379500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3329100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3383100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3503400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3409200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3364300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3361300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3395200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3488500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3282400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3256100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3046500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3250400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3362900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3403500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3422100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3432700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3369000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>996600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1004300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1015500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1013800</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E81" s="3">
         <v>46700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>29800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>24000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>26300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>17200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-15100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>21200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-84900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-50100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>40600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-24400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>10200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-132600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>33400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>37100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>36500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>29600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>35200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>39700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>23300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>83700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-77700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-19400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>35200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>193600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>59900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>101400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>12500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>18000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>16300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>20600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,61 +7996,62 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E83" s="3">
         <v>31300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>43200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>44100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>52800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>32300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>47400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>45200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>45300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>49900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>47400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>45200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>45300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>45100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>45000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>44500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>44400</v>
-      </c>
-      <c r="T83" s="3">
-        <v>44200</v>
       </c>
       <c r="U83" s="3">
         <v>44200</v>
@@ -7864,49 +8063,52 @@
         <v>44200</v>
       </c>
       <c r="X83" s="3">
+        <v>44200</v>
+      </c>
+      <c r="Y83" s="3">
         <v>44000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>43100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>49500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>44900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>48100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>48500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>46800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>48000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>51000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>26600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>17200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>19100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>17200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>80300</v>
+      </c>
+      <c r="E89" s="3">
         <v>80000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>97700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>80100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>52800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>78700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>83200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>70300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>68300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>67600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>108500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>76600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>63100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>97900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>106200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>83700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>68500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>89400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>96900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>93800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>74800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>95500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>85100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>137900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>54000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>77600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>71500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>109900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>101600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>82500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>22700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>31600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>42900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>39300</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,8 +8806,9 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8615,47 +8836,47 @@
       <c r="K91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
+      <c r="L91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M91" s="3">
         <v>-8200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-63400</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
         <v>-20600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-37300</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-33500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-28700</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-25700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-67300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-36200</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>8</v>
@@ -8663,38 +8884,41 @@
       <c r="AA91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AB91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-22500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-25000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E94" s="3">
         <v>18600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-57000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-57300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-61800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>59900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>113200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-31200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-57000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-90900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-37200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-258800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-41900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-35400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-31600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-29100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-69800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-35700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-19300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>311500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>6300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>57800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-19400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>219500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-516400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>120600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-296800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-5400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-31200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-82500</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,22 +9286,23 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>71400</v>
+      </c>
+      <c r="E96" s="3">
         <v>71000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>70300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>69500</v>
-      </c>
-      <c r="G96" s="3">
-        <v>69400</v>
       </c>
       <c r="H96" s="3">
         <v>69400</v>
@@ -9083,7 +9317,7 @@
         <v>69400</v>
       </c>
       <c r="L96" s="3">
-        <v>-69300</v>
+        <v>69400</v>
       </c>
       <c r="M96" s="3">
         <v>-69300</v>
@@ -9095,64 +9329,64 @@
         <v>-69300</v>
       </c>
       <c r="P96" s="3">
+        <v>-69300</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-68600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-66300</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-64800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-63200</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-62600</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-61700</v>
       </c>
       <c r="V96" s="3">
         <v>-61700</v>
       </c>
       <c r="W96" s="3">
+        <v>-61700</v>
+      </c>
+      <c r="X96" s="3">
         <v>-92400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-88200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-85500</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-81500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-80300</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-80200</v>
       </c>
       <c r="AC96" s="3">
         <v>-80200</v>
       </c>
       <c r="AD96" s="3">
+        <v>-80200</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-81900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-82800</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-95300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-26100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-30700</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-30000</v>
       </c>
       <c r="AJ96" s="3">
         <v>-30000</v>
@@ -9160,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>-30000</v>
       </c>
+      <c r="AL96" s="3">
+        <v>-30000</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-101200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-101000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-14000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-46400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-20200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-136400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-68500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-196100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-91600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>56000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-112500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-274600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>371600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-69300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-60100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-60400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-90500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>8900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-50400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-83500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-424800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-87500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-212800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-138400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-161800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-114400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>341000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>317900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-16700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-43300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-5000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>600</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-100</v>
-      </c>
-      <c r="R101" s="3">
-        <v>100</v>
       </c>
       <c r="S101" s="3">
         <v>100</v>
       </c>
       <c r="T101" s="3">
+        <v>100</v>
+      </c>
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-200</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>100</v>
       </c>
-      <c r="AI101" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
         <v>-700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-37400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>26700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-23600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>19200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>22800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-40400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>42200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-86600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-435500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>477500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>44400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-36000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>23700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>5000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-25600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>13300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>9500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-17800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>24800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-27000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-79900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-86100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>167500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-529300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>544100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>20700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-12700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>6000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-84200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBRA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBRA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
   <si>
     <t>SBRA</t>
   </si>
@@ -656,492 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>190000</v>
+      </c>
+      <c r="E8" s="3">
         <v>183800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>183000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>178200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>176200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>166200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>162600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>161000</v>
-      </c>
-      <c r="K8" s="3">
-        <v>160500</v>
       </c>
       <c r="L8" s="3">
         <v>160500</v>
       </c>
       <c r="M8" s="3">
+        <v>160500</v>
+      </c>
+      <c r="N8" s="3">
         <v>165000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>140800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>156000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>163100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>135700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>128600</v>
-      </c>
-      <c r="S8" s="3">
-        <v>152400</v>
       </c>
       <c r="T8" s="3">
         <v>152400</v>
       </c>
       <c r="U8" s="3">
+        <v>152400</v>
+      </c>
+      <c r="V8" s="3">
         <v>151500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>142100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>153900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>149300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>155800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>149800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>152500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>136800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>139200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>151800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>166300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>166100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>166500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>111800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>64700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>62700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>61800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>61900</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E9" s="3">
         <v>59800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>59700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>58400</v>
       </c>
-      <c r="G9" s="3">
-        <v>54600</v>
-      </c>
       <c r="H9" s="3">
+        <v>54700</v>
+      </c>
+      <c r="I9" s="3">
         <v>53900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>49500</v>
-      </c>
-      <c r="J9" s="3">
-        <v>49200</v>
       </c>
       <c r="K9" s="3">
         <v>49200</v>
       </c>
       <c r="L9" s="3">
+        <v>49200</v>
+      </c>
+      <c r="M9" s="3">
         <v>47600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>39200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>36700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>34000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>33100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>30900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>30000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>28500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>28000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>26900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>26500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>26300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>27000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>26000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>24000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>24200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>12000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>12500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>12600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>12300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>12100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>5100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2400</v>
-      </c>
-      <c r="AK9" s="3">
-        <v>1400</v>
       </c>
       <c r="AL9" s="3">
         <v>1400</v>
       </c>
+      <c r="AM9" s="3">
+        <v>1400</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>129100</v>
+      </c>
+      <c r="E10" s="3">
         <v>124000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>123200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>119900</v>
       </c>
-      <c r="G10" s="3">
-        <v>121600</v>
-      </c>
       <c r="H10" s="3">
+        <v>121500</v>
+      </c>
+      <c r="I10" s="3">
         <v>112300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>113100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>111800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>111300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>112900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>125800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>104100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>122000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>130000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>104800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>98600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>123900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>124400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>124600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>115600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>127600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>122300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>129800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>125800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>128300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>124800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>126700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>139200</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>154000</v>
       </c>
       <c r="AF10" s="3">
         <v>154000</v>
       </c>
       <c r="AG10" s="3">
+        <v>154000</v>
+      </c>
+      <c r="AH10" s="3">
         <v>160600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>106700</v>
-      </c>
-      <c r="AI10" s="3">
-        <v>60300</v>
       </c>
       <c r="AJ10" s="3">
         <v>60300</v>
       </c>
       <c r="AK10" s="3">
+        <v>60300</v>
+      </c>
+      <c r="AL10" s="3">
         <v>60400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,107 +1417,110 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-6800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5700</v>
       </c>
-      <c r="G14" s="3">
-        <v>13600</v>
-      </c>
       <c r="H14" s="3">
+        <v>13500</v>
+      </c>
+      <c r="I14" s="3">
         <v>2200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>8000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>42300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>29800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>21200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>61000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>11700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>43400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2200</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>1700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>6000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>2100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>8300</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>14600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-45100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>103100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>2900</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>600</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
@@ -1510,64 +1530,67 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>43600</v>
+      </c>
+      <c r="E15" s="3">
         <v>43500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>42300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>42700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>41700</v>
-      </c>
-      <c r="H15" s="3">
-        <v>42900</v>
       </c>
       <c r="I15" s="3">
         <v>42900</v>
       </c>
       <c r="J15" s="3">
+        <v>42900</v>
+      </c>
+      <c r="K15" s="3">
         <v>43200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>44100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>52800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>49900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>47400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>45200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>45300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>45100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>45000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>44500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>44400</v>
-      </c>
-      <c r="U15" s="3">
-        <v>44200</v>
       </c>
       <c r="V15" s="3">
         <v>44200</v>
@@ -1579,49 +1602,52 @@
         <v>44200</v>
       </c>
       <c r="Y15" s="3">
+        <v>44200</v>
+      </c>
+      <c r="Z15" s="3">
         <v>44000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>43100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>49500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>44900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>48100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>48500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>46800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>48000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>51600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>25900</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>17200</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>19100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>17200</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>117000</v>
+      </c>
+      <c r="E17" s="3">
         <v>116000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>115100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>113500</v>
       </c>
-      <c r="G17" s="3">
-        <v>109000</v>
-      </c>
       <c r="H17" s="3">
+        <v>109100</v>
+      </c>
+      <c r="I17" s="3">
         <v>108700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>109100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>103200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>102800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>110900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>153900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>186800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>129700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>117200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>160300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>115200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>110900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>114700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>111800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>114000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>112000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>111500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>116500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>125300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>67000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>211100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>141700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>115500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>105500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>105900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>109500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>97500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>49000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>45800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>40800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E18" s="3">
         <v>67800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>67900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>64700</v>
       </c>
-      <c r="G18" s="3">
-        <v>67200</v>
-      </c>
       <c r="H18" s="3">
+        <v>67100</v>
+      </c>
+      <c r="I18" s="3">
         <v>57500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>53600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>57800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>57700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>49600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-46000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>26300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>45900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-24600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>41500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>37700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>39700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>28100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>41900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>37800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>39300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>24500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>85500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-74300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>36300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>60800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>60200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>57000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>14300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>15700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>16900</v>
-      </c>
-      <c r="AK18" s="3">
-        <v>21000</v>
       </c>
       <c r="AL18" s="3">
         <v>21000</v>
       </c>
+      <c r="AM18" s="3">
+        <v>21000</v>
+      </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,261 +1950,268 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-13700</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>2000</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>-96000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-9200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-3100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-173500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>8200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-11900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-15700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>140600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>47400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>2100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>2400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>130300</v>
+      </c>
+      <c r="E21" s="3">
         <v>111300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>110200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>107500</v>
       </c>
-      <c r="G21" s="3">
-        <v>109000</v>
-      </c>
       <c r="H21" s="3">
+        <v>108900</v>
+      </c>
+      <c r="I21" s="3">
         <v>100300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>96500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>99100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>101800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>102400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-34900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-2100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>62200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>86100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>21300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>55400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-87600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>78500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>80600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>80500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>74300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>80400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>84900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>67200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>134000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-32100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>29900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>84400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>248200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>111000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>155400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>41400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>37900</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>38100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>40600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>27500</v>
+      </c>
+      <c r="E22" s="3">
         <v>27100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>27600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>29500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>29300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>28400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>27900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>28200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>28300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>28500</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -2247,135 +2287,141 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E23" s="3">
         <v>40700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>47100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>29500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>24400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>26700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>17600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>21500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-84800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-49500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>17100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>40900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-23800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>10300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-132100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>34100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>36500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>36300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>30100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>36300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>40900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>24100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>84500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-77100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-18200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>36000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>201400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>63000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>104500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>14900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>20700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>19000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>23400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E24" s="3">
         <v>400</v>
       </c>
       <c r="F24" s="3">
+        <v>400</v>
+      </c>
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>400</v>
-      </c>
-      <c r="H24" s="3">
-        <v>500</v>
       </c>
       <c r="I24" s="3">
         <v>500</v>
@@ -2384,91 +2430,94 @@
         <v>500</v>
       </c>
       <c r="K24" s="3">
+        <v>500</v>
+      </c>
+      <c r="L24" s="3">
         <v>300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>600</v>
-      </c>
-      <c r="O24" s="3">
-        <v>300</v>
       </c>
       <c r="P24" s="3">
         <v>300</v>
       </c>
       <c r="Q24" s="3">
+        <v>300</v>
+      </c>
+      <c r="R24" s="3">
         <v>500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>600</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>500</v>
       </c>
       <c r="AG24" s="3">
         <v>500</v>
       </c>
       <c r="AH24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AI24" s="3">
         <v>-200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>65500</v>
+      </c>
+      <c r="E26" s="3">
         <v>40300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>46700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>29800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>24000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>26300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>17200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-15100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>21200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-84900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-50100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>16800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>40600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-24400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>10200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-132600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>33400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>37100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>36500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>29600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>35200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>39700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>23300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>83700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-77700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-19400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>35200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>200800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>62500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>104000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>15100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>20500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>18800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>23200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>65500</v>
+      </c>
+      <c r="E27" s="3">
         <v>40300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>46700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>29800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>24000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>26300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>17200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-15100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>21200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-84900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-50100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>16800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>40600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-24400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>10200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-132600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>33400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>37100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>36500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>29600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>35200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>39700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>23300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>83700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-77700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-19400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>35200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>193600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>59900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>101400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>12500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>16300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>20600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,228 +3304,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>13700</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2000</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>96000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>9200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>3100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>173500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-8200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>11900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>15700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-140600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-47400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>65500</v>
+      </c>
+      <c r="E33" s="3">
         <v>40300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>46700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>29800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>24000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>26300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>17200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-15100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>21200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-84900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-50100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>16800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>40600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-24400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>10200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-132600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>33400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>37100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>36500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>29600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>35200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>39700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>23300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>83700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-77700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-19400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>35200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>193600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>59900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>101400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>12500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>16300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>20600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>65500</v>
+      </c>
+      <c r="E35" s="3">
         <v>40300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>46700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>29800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>24000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>26300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>17200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-15100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>21200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-84900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-50100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>16800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>40600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-24400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>10200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-132600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>33400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>37100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>36500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>29600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>35200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>39700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>23300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>83700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-77700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-19400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>35200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>193600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>59900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>101400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>12500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>16300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>20600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,151 +3958,155 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>95200</v>
+      </c>
+      <c r="E41" s="3">
         <v>22700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>60500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>63000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>36400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>59900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>41300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>33300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>27200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>33500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>49300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>26300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>67200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>24800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>112000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>546300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>69300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>24900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>59100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>35000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>28300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>54100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>39100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>29400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>47600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>22900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>50200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>36300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>38800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>46400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>518600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>30900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>13200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>12800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>25700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E42" s="3">
         <v>15200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>21500</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>27000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>27100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>18900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>39300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>31100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>19800</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -4092,41 +4182,44 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E43" s="3">
         <v>46600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>149100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>46400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>46100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>43700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>147100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>42000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>42300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>37400</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -4202,8 +4295,11 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4234,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4312,8 +4408,11 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4344,8 +4443,8 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
+      <c r="M45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
@@ -4404,59 +4503,62 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-      <c r="AG45" s="3" t="s">
-        <v>8</v>
+      <c r="AG45" s="3">
+        <v>0</v>
       </c>
       <c r="AH45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AI45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>141200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>126000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>125300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>116400</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>149000</v>
+      </c>
+      <c r="E46" s="3">
         <v>90800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>237000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>125700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>115400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>136700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>212700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>120200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>105800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>95900</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4532,326 +4634,335 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>189500</v>
+      </c>
+      <c r="E47" s="3">
         <v>182800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>182900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>190600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>187100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>191800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>194700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>192700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>196100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>192100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>546400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>597900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>615300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>491000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>495800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>215800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>219200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>385000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>391600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>397600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>379700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>400100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>426800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>432600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>439400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>444900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>453800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>454700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>456200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>455800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>114400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>149800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>94200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>96500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>96000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>94500</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4486100</v>
+      </c>
+      <c r="E48" s="3">
         <v>4495000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4520700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4581500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4576900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4588700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4628900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4603000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4751900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4797000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4959300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5018900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5045100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5156100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5162900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5228700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5269400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5279400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5285000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5306300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5358500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5363200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5350700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5354400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5388400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5447200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5853500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5975600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5993700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6108800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5994400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5972800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1995900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1993600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2009900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1999800</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E49" s="3">
         <v>24800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>27500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>28800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>27700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>28300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>30900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>32700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>36000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>39400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>40100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>48300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>49800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>52900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>54100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>76400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>79700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>81500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>82800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>85900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>93500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>96800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>101500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>105000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>108900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>119700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>131100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>142900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>156300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>161400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>167100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>262800</v>
-      </c>
-      <c r="AI49" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AJ49" s="3" t="s">
         <v>8</v>
@@ -4862,8 +4973,11 @@
       <c r="AL49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>143200</v>
+      </c>
+      <c r="E52" s="3">
         <v>104200</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="F52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>103900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>108500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>109900</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>112900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>115500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>112900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4900</v>
-      </c>
-      <c r="O52" s="3">
-        <v>4400</v>
       </c>
       <c r="P52" s="3">
         <v>4400</v>
       </c>
       <c r="Q52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="R52" s="3">
         <v>3900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5100</v>
-      </c>
-      <c r="S52" s="3">
-        <v>4600</v>
       </c>
       <c r="T52" s="3">
         <v>4600</v>
       </c>
       <c r="U52" s="3">
+        <v>4600</v>
+      </c>
+      <c r="V52" s="3">
         <v>6400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>8600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>8400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>10000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>10200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>9900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>280500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>103200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>186800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>11800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>68800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>12500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>9400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>11200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>9000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5328000</v>
+      </c>
+      <c r="E54" s="3">
         <v>5233200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5303700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5366100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5351100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5374400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5386200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5380600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5524300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5556300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5747700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5844900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5961400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5884900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5966700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6209500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5822100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5963800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5985600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5991600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6023600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6092300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6069300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6068000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6123200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6455100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6665300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6910300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7028100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6984600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7032300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6588300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2254000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>2240100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>2265900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>2239400</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,151 +5622,155 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>65600</v>
+      </c>
+      <c r="E57" s="3">
         <v>61800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>67800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>71300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>62500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>59000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>73800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>78300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>74700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>94000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>124100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>123200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>101100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>92900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>121500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>108600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>103300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>105900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>130200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>125600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>143300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>112500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>98400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>92100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>90800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>72900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>94800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>86900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>105300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>102400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>102500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>116100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>37100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>33400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>39600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E58" s="3">
         <v>2700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2500</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1500</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5712,76 +5846,79 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E59" s="3">
         <v>21000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>30800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>19500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>20800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>34200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>28600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>30800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>27600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>22000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>25400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>21500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>16100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>17600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>16100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>18100</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y59" s="3">
-        <v>9800</v>
+      <c r="Y59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z59" s="3">
         <v>9800</v>
@@ -5790,16 +5927,16 @@
         <v>9800</v>
       </c>
       <c r="AB59" s="3">
+        <v>9800</v>
+      </c>
+      <c r="AC59" s="3">
         <v>10000</v>
-      </c>
-      <c r="AC59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE59" s="3">
-        <v>0</v>
+      <c r="AE59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF59" s="3">
         <v>0</v>
@@ -5822,41 +5959,44 @@
       <c r="AL59" s="3">
         <v>0</v>
       </c>
+      <c r="AM59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>107000</v>
+      </c>
+      <c r="E60" s="3">
         <v>106700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>118300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>115200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>102200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>102900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>124500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>128500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>122900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>144500</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5932,151 +6072,157 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2485700</v>
+      </c>
+      <c r="E61" s="3">
         <v>2399200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2422300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2477800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2457300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2473300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2426600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2349000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2419000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2395100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2506800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2446900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2480200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2357500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2394500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2702100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2266300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2281600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2372400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2423000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2455300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2479300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2402100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2603100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2686000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3230200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3232000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3368600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3423800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3361100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3394500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3005500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1220100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1202400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1210700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1187400</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>23800</v>
+      </c>
+      <c r="E62" s="3">
         <v>25000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>21700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>28300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>29700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>31100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>32500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>34200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>38700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>40500</v>
       </c>
-      <c r="M62" s="3">
-        <v>0</v>
-      </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
@@ -6152,8 +6298,11 @@
       <c r="AL62" s="3">
         <v>0</v>
       </c>
+      <c r="AM62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2616500</v>
+      </c>
+      <c r="E66" s="3">
         <v>2531000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2562400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2621300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2589100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2607300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2583600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2511700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2580600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2580100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2691300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2636200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2643700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2523400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2587200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2880400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2439100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2460400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2576400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2627300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2662300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2697100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2580800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2785600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2867100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3408700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3414900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3547400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3624600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3562400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3599500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3219200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1257300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1235800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1250300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1225600</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6942,7 +7110,7 @@
         <v>0</v>
       </c>
       <c r="AF70" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG70" s="3">
         <v>100</v>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>100</v>
       </c>
+      <c r="AM70" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,8 +7243,11 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7104,86 +7278,89 @@
       <c r="L72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N72" s="3">
         <v>-1451900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-1296900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-1177000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1124100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1095200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1001200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-944500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-746500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-716200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-689800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-663900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-631300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-573300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-523700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-460800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-462600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-271600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-171100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-125600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-238600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-217200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-225500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-214100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-203600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-192200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-185000</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2711500</v>
+      </c>
+      <c r="E76" s="3">
         <v>2702200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2741300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2744800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2762000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2767200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2802500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2868900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2943700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2976200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3056400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3208700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3317700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3361500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3379500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3329100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3383100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3503400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3409200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3364300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3361300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3395200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3488500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3282400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3256100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3046500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3250400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3362900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3403500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3422100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3432700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3369000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>996600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1004300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1015500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1013800</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>65500</v>
+      </c>
+      <c r="E81" s="3">
         <v>40300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>46700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>29800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>24000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>26300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>17200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-15100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>21200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-84900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-50100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>16800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>40600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-24400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>10200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-132600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>33400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>37100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>36500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>29600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>35200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>39700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>23300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>83700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-77700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-19400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>35200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>193600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>59900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>101400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>12500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>18000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>16300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>20600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,64 +8195,65 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>41700</v>
+      </c>
+      <c r="E83" s="3">
         <v>42900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>31300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>43200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>44100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>52800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>32300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>47400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>45200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>45300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>49900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>47400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>45200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>45300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>45100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>45000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>44500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>44400</v>
-      </c>
-      <c r="U83" s="3">
-        <v>44200</v>
       </c>
       <c r="V83" s="3">
         <v>44200</v>
@@ -8066,49 +8265,52 @@
         <v>44200</v>
       </c>
       <c r="Y83" s="3">
+        <v>44200</v>
+      </c>
+      <c r="Z83" s="3">
         <v>44000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>43100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>49500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>44900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>48100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>48500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>46800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>48000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>51000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>26600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>17200</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>19100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>17200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E89" s="3">
         <v>80300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>80000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>97700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>80100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>52800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>78700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>83200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>70300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>68300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>67600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>108500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>76600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>63100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>97900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>106200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>83700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>68500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>89400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>96900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>93800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>74800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>95500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>85100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>137900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>54000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>77600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>71500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>109900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>101600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>82500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>22700</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>31600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>42900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>39300</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,8 +9027,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8839,47 +9060,47 @@
       <c r="L91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M91" s="3">
+      <c r="M91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N91" s="3">
         <v>-8200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-63400</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-20600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-37300</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-33500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-28700</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
         <v>0</v>
       </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-25700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-67300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-36200</v>
-      </c>
-      <c r="Z91" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA91" s="3" t="s">
         <v>8</v>
@@ -8887,38 +9108,41 @@
       <c r="AB91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AC91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-22500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-25000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-100</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-45100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-16400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>18600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-57000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-57300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-61800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>59900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>113200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-31200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-57000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-90900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-37200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-258800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-41900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-35400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-31600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-29100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-69800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-35700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-19300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>311500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>6300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>57800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-19400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>219500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-516400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>120600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-296800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-5400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-31200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-82500</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,8 +9520,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9296,16 +9530,16 @@
         <v>71400</v>
       </c>
       <c r="E96" s="3">
+        <v>71400</v>
+      </c>
+      <c r="F96" s="3">
         <v>71000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>70300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>69500</v>
-      </c>
-      <c r="H96" s="3">
-        <v>69400</v>
       </c>
       <c r="I96" s="3">
         <v>69400</v>
@@ -9320,7 +9554,7 @@
         <v>69400</v>
       </c>
       <c r="M96" s="3">
-        <v>-69300</v>
+        <v>69400</v>
       </c>
       <c r="N96" s="3">
         <v>-69300</v>
@@ -9332,64 +9566,64 @@
         <v>-69300</v>
       </c>
       <c r="Q96" s="3">
+        <v>-69300</v>
+      </c>
+      <c r="R96" s="3">
         <v>-68600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-66300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-64800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-63200</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-62600</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-61700</v>
       </c>
       <c r="W96" s="3">
         <v>-61700</v>
       </c>
       <c r="X96" s="3">
+        <v>-61700</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-92400</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-88200</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-85500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-81500</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-80300</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-80200</v>
       </c>
       <c r="AD96" s="3">
         <v>-80200</v>
       </c>
       <c r="AE96" s="3">
+        <v>-80200</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-81900</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-82800</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-95300</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-26100</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-30700</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-30000</v>
       </c>
       <c r="AK96" s="3">
         <v>-30000</v>
@@ -9397,8 +9631,11 @@
       <c r="AL96" s="3">
         <v>-30000</v>
       </c>
+      <c r="AM96" s="3">
+        <v>-30000</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>36700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-101200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-101000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-14000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-46400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-20200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-136400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-68500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-196100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-91600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>56000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-112500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-274600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>371600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-69300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-60100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-60400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-90500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>8900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-50400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-83500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-424800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-87500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-212800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-138400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-161800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-114400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>341000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>317900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-16700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-43300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-5000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
         <v>-600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>600</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-100</v>
-      </c>
-      <c r="S101" s="3">
-        <v>100</v>
       </c>
       <c r="T101" s="3">
         <v>100</v>
       </c>
       <c r="U101" s="3">
+        <v>100</v>
+      </c>
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-200</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>100</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
       <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
         <v>-700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>72800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-37400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>26700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-23600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>19200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>22800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-40400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>42200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-86600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-435500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>477500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>44400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-36000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>23700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>5000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-25600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>13300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>9500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-17800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>24800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-27000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-79900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-86100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>167500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-529300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>544100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>20700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-12700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>6000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-84200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBRA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBRA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
   <si>
     <t>SBRA</t>
   </si>
@@ -656,518 +656,530 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>210800</v>
+      </c>
+      <c r="E8" s="3">
         <v>191300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>190000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>183800</v>
       </c>
-      <c r="G8" s="3">
-        <v>183000</v>
-      </c>
       <c r="H8" s="3">
+        <v>182100</v>
+      </c>
+      <c r="I8" s="3">
         <v>178200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>176200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>166200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>162600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>161000</v>
-      </c>
-      <c r="M8" s="3">
-        <v>160500</v>
       </c>
       <c r="N8" s="3">
         <v>160500</v>
       </c>
       <c r="O8" s="3">
+        <v>160500</v>
+      </c>
+      <c r="P8" s="3">
         <v>165000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>140800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>156000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>163100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>135700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>128600</v>
-      </c>
-      <c r="U8" s="3">
-        <v>152400</v>
       </c>
       <c r="V8" s="3">
         <v>152400</v>
       </c>
       <c r="W8" s="3">
+        <v>152400</v>
+      </c>
+      <c r="X8" s="3">
         <v>151500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>142100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>153900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>149300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>155800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>149800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>152500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>136800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>139200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>151800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>166300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>166100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>166500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>111800</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>64700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>62700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>61800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>61900</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E9" s="3">
         <v>69400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>60900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>59800</v>
       </c>
-      <c r="G9" s="3">
-        <v>59700</v>
-      </c>
       <c r="H9" s="3">
+        <v>59200</v>
+      </c>
+      <c r="I9" s="3">
         <v>58500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>54700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>53900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>49500</v>
-      </c>
-      <c r="L9" s="3">
-        <v>49200</v>
       </c>
       <c r="M9" s="3">
         <v>49200</v>
       </c>
       <c r="N9" s="3">
+        <v>49200</v>
+      </c>
+      <c r="O9" s="3">
         <v>47600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>39200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>36700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>34000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>33100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>30900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>30000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>28500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>28000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>26900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>26500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>26300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>27000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>26000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>24000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>24200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>12000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>12500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>12600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>12300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>12100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>5900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>5100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2400</v>
-      </c>
-      <c r="AM9" s="3">
-        <v>1400</v>
       </c>
       <c r="AN9" s="3">
         <v>1400</v>
       </c>
+      <c r="AO9" s="3">
+        <v>1400</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>130700</v>
+      </c>
+      <c r="E10" s="3">
         <v>121800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>129100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>124000</v>
       </c>
-      <c r="G10" s="3">
-        <v>123200</v>
-      </c>
       <c r="H10" s="3">
+        <v>122800</v>
+      </c>
+      <c r="I10" s="3">
         <v>119800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>121500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>112300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>113100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>111800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>111300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>112900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>125800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>104100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>122000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>130000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>104800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>98600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>123900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>124400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>124600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>115600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>127600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>122300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>129800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>125800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>128300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>124800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>126700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>139200</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>154000</v>
       </c>
       <c r="AH10" s="3">
         <v>154000</v>
       </c>
       <c r="AI10" s="3">
+        <v>154000</v>
+      </c>
+      <c r="AJ10" s="3">
         <v>160600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>106700</v>
-      </c>
-      <c r="AK10" s="3">
-        <v>60300</v>
       </c>
       <c r="AL10" s="3">
         <v>60300</v>
       </c>
       <c r="AM10" s="3">
+        <v>60300</v>
+      </c>
+      <c r="AN10" s="3">
         <v>60400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1220,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1324,8 +1337,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,113 +1456,116 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E14" s="3">
         <v>7600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-6900</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
-        <v>-6800</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="I14" s="3">
         <v>5600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>13500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>8000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>42300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>7800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>29800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>21200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>61000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>11700</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-2000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>43400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2200</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>1700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>6000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>2100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>300</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>8300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>14600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-45100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>103100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>2900</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>500</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>600</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
         <v>0</v>
       </c>
@@ -1556,70 +1575,73 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>51400</v>
+      </c>
+      <c r="E15" s="3">
         <v>48500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>43600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>43500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>42300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>42700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>41700</v>
-      </c>
-      <c r="J15" s="3">
-        <v>42900</v>
       </c>
       <c r="K15" s="3">
         <v>42900</v>
       </c>
       <c r="L15" s="3">
+        <v>42900</v>
+      </c>
+      <c r="M15" s="3">
         <v>43200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>44100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>52800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>49900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>47400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>45200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>45300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>45100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>45000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>44500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>44400</v>
-      </c>
-      <c r="W15" s="3">
-        <v>44200</v>
       </c>
       <c r="X15" s="3">
         <v>44200</v>
@@ -1631,49 +1653,52 @@
         <v>44200</v>
       </c>
       <c r="AA15" s="3">
+        <v>44200</v>
+      </c>
+      <c r="AB15" s="3">
         <v>44000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>43100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>49500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>44900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>48100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>48500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>46800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>48000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>51600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>25900</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>17200</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>19100</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>17200</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1736,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>160800</v>
+      </c>
+      <c r="E17" s="3">
         <v>131900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>117000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>116000</v>
       </c>
-      <c r="G17" s="3">
-        <v>115100</v>
-      </c>
       <c r="H17" s="3">
+        <v>114500</v>
+      </c>
+      <c r="I17" s="3">
         <v>113600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>109100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>108700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>109100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>103200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>102800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>110900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>153900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>186800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>129700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>117200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>160300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>115200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>110900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>114700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>111800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>114000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>112000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>111500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>116500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>125300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>67000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>211100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>141700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>115500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>105500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>105900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>109500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>97500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>49000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>45800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>40800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E18" s="3">
         <v>59400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>73000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>67800</v>
       </c>
-      <c r="G18" s="3">
-        <v>67900</v>
-      </c>
       <c r="H18" s="3">
+        <v>67600</v>
+      </c>
+      <c r="I18" s="3">
         <v>64600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>67100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>57500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>53600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>57800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>57700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>49600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>11100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-46000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>26300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>45900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-24600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>41500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>37700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>39700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>28100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>41900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>37800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>39300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>24500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>85500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-74300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>36300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>60800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>60200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>57000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>14300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>15700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>16900</v>
-      </c>
-      <c r="AM18" s="3">
-        <v>21000</v>
       </c>
       <c r="AN18" s="3">
         <v>21000</v>
       </c>
+      <c r="AO18" s="3">
+        <v>21000</v>
+      </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,279 +2017,286 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3">
         <v>-13700</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3">
         <v>-100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>2000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3">
         <v>-96000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-9200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-173500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>8200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-11900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-15700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>140600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>47400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>5000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>2100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>2400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>97700</v>
+      </c>
+      <c r="E21" s="3">
         <v>107900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>130300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>111300</v>
       </c>
-      <c r="G21" s="3">
-        <v>110200</v>
-      </c>
       <c r="H21" s="3">
+        <v>109900</v>
+      </c>
+      <c r="I21" s="3">
         <v>107400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>108900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>100300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>96500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>99100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>101800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>102400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-34900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>62200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>86100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>21300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>55400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-87600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>78500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>80600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>80500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>74300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>80400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>84900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>67200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>134000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-32100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>29900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>84400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>248200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>111000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>155400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>41400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>37900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>38100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>40600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E22" s="3">
         <v>28900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>27500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>27100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>27600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>29500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>29300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>28400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>27900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>28200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>28300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>28500</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -2333,147 +2372,153 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E23" s="3">
         <v>23000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>66000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>40700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>47100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>29500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>24400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>26700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>17600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>21500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-8800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-84800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-49500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>17100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>40900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-23800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>10300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-132100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>34100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>36500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>36300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>30100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>36300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>40900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>24100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>84500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-77100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-18200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>36000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>201400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>63000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>104500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>14900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>20700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>19000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>23400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>500</v>
+      </c>
+      <c r="E24" s="3">
         <v>400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
-      </c>
-      <c r="F24" s="3">
-        <v>400</v>
       </c>
       <c r="G24" s="3">
         <v>400</v>
       </c>
       <c r="H24" s="3">
+        <v>400</v>
+      </c>
+      <c r="I24" s="3">
         <v>-300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
-      </c>
-      <c r="J24" s="3">
-        <v>500</v>
       </c>
       <c r="K24" s="3">
         <v>500</v>
@@ -2482,91 +2527,94 @@
         <v>500</v>
       </c>
       <c r="M24" s="3">
+        <v>500</v>
+      </c>
+      <c r="N24" s="3">
         <v>300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>600</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>300</v>
       </c>
       <c r="R24" s="3">
         <v>300</v>
       </c>
       <c r="S24" s="3">
+        <v>300</v>
+      </c>
+      <c r="T24" s="3">
         <v>500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>600</v>
-      </c>
-      <c r="AH24" s="3">
-        <v>500</v>
       </c>
       <c r="AI24" s="3">
         <v>500</v>
       </c>
       <c r="AJ24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AK24" s="3">
         <v>-200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>200</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2729,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E26" s="3">
         <v>22500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>65500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>40300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>46700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>29800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>24000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>26300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>17200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-15100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>21200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-84900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-50100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>16800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>40600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-24400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>10200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-132600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>33400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>37100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>36500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>29600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>35200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>39700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>23300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>83700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-77700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-19400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>35200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>200800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>62500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>104000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>15100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>20500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>18800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>23200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E27" s="3">
         <v>22500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>65500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>40300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>46700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>29800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>24000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>26300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>17200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-15100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>21200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-84900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-50100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>16800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>40600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-24400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>10200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-132600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>33400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>37100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>36500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>29600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>35200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>39700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>23300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>83700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-77700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-19400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>35200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>193600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>59900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>101400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>12500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>18000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>16300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>20600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3086,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3145,8 +3205,11 @@
       <c r="AN29" s="3">
         <v>0</v>
       </c>
+      <c r="AO29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3324,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,240 +3443,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3">
         <v>13700</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3">
         <v>100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-2000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3">
         <v>96000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>9200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>173500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>11900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>15700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-140600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-47400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E33" s="3">
         <v>22500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>65500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>40300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>46700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>29800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>24000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>26300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>17200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-15100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>21200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-84900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-50100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>16800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>40600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-24400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>10200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-132600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>33400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>37100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>36500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>29600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>35200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>39700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>23300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>83700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-77700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-19400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>35200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>193600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>59900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>101400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>12500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>18000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>16300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>20600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3800,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E35" s="3">
         <v>22500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>65500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>40300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>46700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>29800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>24000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>26300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>17200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-15100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>21200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-84900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-50100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>16800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>40600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-24400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>10200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-132600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>33400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>37100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>36500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>29600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>35200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>39700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>23300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>83700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-77700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-19400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>35200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>193600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>59900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>101400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>12500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>18000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>16300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>20600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4088,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,163 +4131,167 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>71500</v>
+      </c>
+      <c r="E41" s="3">
         <v>200600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>95200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>22700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>60500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>63000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>36400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>59900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>41300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>33300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>27200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>33500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>49300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>26300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>67200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>24800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>112000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>546300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>69300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>24900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>59100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>35000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>28300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>54100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>39100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>29400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>47600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>22900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>50200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>36300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>38800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>46400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>518600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>30900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>13200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>12800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>25700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E42" s="3">
         <v>3800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>5100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>15200</v>
       </c>
-      <c r="G42" s="3">
-        <v>21500</v>
-      </c>
       <c r="H42" s="3">
+        <v>20400</v>
+      </c>
+      <c r="I42" s="3">
         <v>10300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>27000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>27100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>18900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>39300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>31100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>19800</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4278,47 +4367,50 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>134600</v>
+      </c>
+      <c r="E43" s="3">
         <v>139600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>42300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>46600</v>
       </c>
-      <c r="G43" s="3">
-        <v>149100</v>
-      </c>
       <c r="H43" s="3">
+        <v>150200</v>
+      </c>
+      <c r="I43" s="3">
         <v>46400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>46100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>43700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>147100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>42000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>42300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>37400</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -4394,8 +4486,11 @@
       <c r="AN43" s="3">
         <v>0</v>
       </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4432,8 +4527,8 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4510,8 +4605,11 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4548,8 +4646,8 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
+      <c r="O45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P45" s="3">
         <v>0</v>
@@ -4608,65 +4706,68 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-      <c r="AI45" s="3" t="s">
-        <v>8</v>
+      <c r="AI45" s="3">
+        <v>0</v>
       </c>
       <c r="AJ45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AK45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL45" s="3">
         <v>141200</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>126000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>125300</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>116400</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>216100</v>
+      </c>
+      <c r="E46" s="3">
         <v>350900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>149000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>90800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>237000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>125700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>115400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>136700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>212700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>120200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>105800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>95900</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4742,345 +4843,354 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>183500</v>
+      </c>
+      <c r="E47" s="3">
         <v>182000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>189500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>182800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>182900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>190600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>187100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>191800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>194700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>192700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>196100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>192100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>546400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>597900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>615300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>491000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>495800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>215800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>219200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>385000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>391600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>397600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>379700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>400100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>426800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>432600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>439400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>444900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>453800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>454700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>456200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>455800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>114400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>149800</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>94200</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>96500</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>96000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>94500</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4692900</v>
+      </c>
+      <c r="E48" s="3">
         <v>4636400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4486100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4495000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4520700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4581500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4576900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4588700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4628900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4603000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4751900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4797000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4959300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5018900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5045100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5156100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5162900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5228700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5269400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5279400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5285000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5306300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5358500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5363200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5350700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5354400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5388400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5447200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5853500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5975600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5993700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6108800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5994400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>5972800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1995900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1993600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2009900</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1999800</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>65300</v>
+      </c>
+      <c r="E49" s="3">
         <v>59800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>24700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>24800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>27500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>28800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>27700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>28300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>30900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>32700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>36000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>39400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>40100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>48300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>49800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>52900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>54100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>76400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>79700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>81500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>82800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>85900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>93500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>96800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>101500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>105000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>108900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>119700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>131100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>142900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>156300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>161400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>167100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>262800</v>
       </c>
-      <c r="AK49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL49" s="3" t="s">
         <v>8</v>
       </c>
@@ -5090,8 +5200,11 @@
       <c r="AN49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,124 +5438,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E52" s="3">
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3">
         <v>143200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>104200</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3">
         <v>103900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>108500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>109900</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3">
         <v>112900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>115500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>112900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4900</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>4400</v>
       </c>
       <c r="R52" s="3">
         <v>4400</v>
       </c>
       <c r="S52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="T52" s="3">
         <v>3900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5100</v>
-      </c>
-      <c r="U52" s="3">
-        <v>4600</v>
       </c>
       <c r="V52" s="3">
         <v>4600</v>
       </c>
       <c r="W52" s="3">
+        <v>4600</v>
+      </c>
+      <c r="X52" s="3">
         <v>6400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>8600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>8400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>10000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>280500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>103200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>186800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>11800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>68800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>12500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>9400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>11200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>9000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5676,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5493400</v>
+      </c>
+      <c r="E54" s="3">
         <v>5564800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5328000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5233200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5303700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5366100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5351100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5374400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5386200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5380600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5524300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5556300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5747700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5844900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5961400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5884900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5966700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6209500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5822100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5963800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5985600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5991600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>6023600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6092300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6069300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6068000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6123200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6455100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6665300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6910300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>7028100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>6984600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>7032300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>6588300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>2254000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>2240100</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>2265900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>2239400</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5840,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,163 +5883,167 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>73200</v>
+      </c>
+      <c r="E57" s="3">
         <v>71900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>65600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>61800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>67800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>71300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>62500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>59000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>73800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>78300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>74700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>94000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>124100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>123200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>101100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>92900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>121500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>108600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>103300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>105900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>130200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>125600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>143300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>112500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>98400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>92100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>90800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>72900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>94800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>86900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>105300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>102400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>102500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>116100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>37100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>33400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>39600</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E58" s="3">
         <v>3200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2700</v>
       </c>
-      <c r="G58" s="3">
-        <v>3600</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
         <v>1100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2500</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1500</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5986,82 +6119,85 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E59" s="3">
         <v>21000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>22100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
+        <v>25700</v>
+      </c>
+      <c r="I59" s="3">
+        <v>19500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>20800</v>
+      </c>
+      <c r="K59" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L59" s="3">
+        <v>34200</v>
+      </c>
+      <c r="M59" s="3">
+        <v>28600</v>
+      </c>
+      <c r="N59" s="3">
         <v>30800</v>
       </c>
-      <c r="H59" s="3">
-        <v>19500</v>
-      </c>
-      <c r="I59" s="3">
-        <v>20800</v>
-      </c>
-      <c r="J59" s="3">
-        <v>20000</v>
-      </c>
-      <c r="K59" s="3">
-        <v>34200</v>
-      </c>
-      <c r="L59" s="3">
-        <v>28600</v>
-      </c>
-      <c r="M59" s="3">
-        <v>30800</v>
-      </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>27600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>22000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>25400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>21500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>18200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>16100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>17600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>16100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>18100</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA59" s="3">
-        <v>9800</v>
+      <c r="AA59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB59" s="3">
         <v>9800</v>
@@ -6070,16 +6206,16 @@
         <v>9800</v>
       </c>
       <c r="AD59" s="3">
+        <v>9800</v>
+      </c>
+      <c r="AE59" s="3">
         <v>10000</v>
       </c>
-      <c r="AE59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG59" s="3">
-        <v>0</v>
+      <c r="AG59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH59" s="3">
         <v>0</v>
@@ -6102,47 +6238,50 @@
       <c r="AN59" s="3">
         <v>0</v>
       </c>
+      <c r="AO59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>119700</v>
+      </c>
+      <c r="E60" s="3">
         <v>117300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>107000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>106700</v>
       </c>
-      <c r="G60" s="3">
-        <v>118300</v>
-      </c>
       <c r="H60" s="3">
+        <v>109600</v>
+      </c>
+      <c r="I60" s="3">
         <v>115200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>102200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>102900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>124500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>128500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>122900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>144500</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6218,163 +6357,169 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2533100</v>
+      </c>
+      <c r="E61" s="3">
         <v>2597900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2485700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2399200</v>
       </c>
-      <c r="G61" s="3">
-        <v>2422300</v>
-      </c>
       <c r="H61" s="3">
+        <v>2425900</v>
+      </c>
+      <c r="I61" s="3">
         <v>2477800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2457300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2473300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2426600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2349000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2419000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2395100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2506800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2446900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2480200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2357500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2394500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2702100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2266300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2281600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2372400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2423000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2455300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2479300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2402100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2603100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2686000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3230200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3232000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3368600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3423800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3361100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3394500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3005500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1220100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1202400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1210700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1187400</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E62" s="3">
         <v>22600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>23800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>25000</v>
       </c>
-      <c r="G62" s="3">
-        <v>21700</v>
-      </c>
       <c r="H62" s="3">
+        <v>26800</v>
+      </c>
+      <c r="I62" s="3">
         <v>28300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>29700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>31100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>32500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>34200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>38700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>40500</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
-      </c>
       <c r="P62" s="3">
         <v>0</v>
       </c>
@@ -6450,8 +6595,11 @@
       <c r="AN62" s="3">
         <v>0</v>
       </c>
+      <c r="AO62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6714,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6833,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6952,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2669600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2737800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2616500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2531000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2562400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2621300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2589100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2607300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2583600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2511700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2580600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2580100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2691300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2636200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2643700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2523400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2587200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2880400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2439100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2460400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2576400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2627300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2662300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2697100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2580800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2785600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2867100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3408700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3414900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3547400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3624600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3562400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3599500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3219200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1257300</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1235800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1250300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1225600</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7116,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7233,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7352,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7284,7 +7451,7 @@
         <v>0</v>
       </c>
       <c r="AH70" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AI70" s="3">
         <v>100</v>
@@ -7304,8 +7471,11 @@
       <c r="AN70" s="3">
         <v>100</v>
       </c>
+      <c r="AO70" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,8 +7590,11 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7458,86 +7631,89 @@
       <c r="N72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P72" s="3">
         <v>-1451900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-1296900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1177000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1124100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1095200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1001200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-944500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-746500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-716200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-689800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-663900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-631300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-573300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-523700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-460800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-462600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-271600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-171100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-125600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-238600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-217200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-225500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-214100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-203600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-192200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-185000</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7828,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7947,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8066,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2821800</v>
+      </c>
+      <c r="E76" s="3">
         <v>2824900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2711500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2702200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2741300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2744800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2762000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2767200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2802500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2868900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2943700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2976200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3056400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3208700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3317700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3361500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3379500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3329100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3383100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3503400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3409200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3364300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3361300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3395200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3488500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3282400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3256100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3046500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3250400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3362900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3403500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3422100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3432700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3369000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>996600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1004300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1015500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1013800</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8304,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E81" s="3">
         <v>22500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>65500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>40300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>46700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>29800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>24000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>26300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>17200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-15100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>21200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-84900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-50100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>16800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>40600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-24400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>10200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-132600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>33400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>37100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>36500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>29600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>35200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>39700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>23300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>83700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-77700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-19400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>35200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>193600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>59900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>101400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>12500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>18000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>16300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>20600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,70 +8592,71 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E83" s="3">
         <v>42700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>41700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>42900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>31300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>43200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>44100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>52800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>32300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>47400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>45200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>45300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>49900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>47400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>45200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>45300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>45100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>45000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>44500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>44400</v>
-      </c>
-      <c r="W83" s="3">
-        <v>44200</v>
       </c>
       <c r="X83" s="3">
         <v>44200</v>
@@ -8470,49 +8668,52 @@
         <v>44200</v>
       </c>
       <c r="AA83" s="3">
+        <v>44200</v>
+      </c>
+      <c r="AB83" s="3">
         <v>44000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>43100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>49500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>44900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>48100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>48500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>46800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>48000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>51000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>26600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>17200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>19100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>17200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8828,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8947,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9066,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9185,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9304,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>87400</v>
+      </c>
+      <c r="E89" s="3">
         <v>100000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>81000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>80300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>80000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>97700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>80100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>52800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>78700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>83200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>70300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>68300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>67600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>108500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>76600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>63100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>97900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>106200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>83700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>68500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>89400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>96900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>93800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>74800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>95500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>85100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>137900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>54000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>77600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>71500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>109900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>101600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>82500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>22700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>31600</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>42900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>39300</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,8 +9468,9 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9287,86 +9507,89 @@
       <c r="N91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O91" s="3">
+      <c r="O91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P91" s="3">
         <v>-8200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-63400</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
         <v>-20600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-37300</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-33500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-28700</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
       <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-25700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-67300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-36200</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AD91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-22500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-25000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9704,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +9823,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-116500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-199800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-45100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-16400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>18600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-57000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-57300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-61800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>59900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>113200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-31200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-57000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-90900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-37200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-258800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-41900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-35400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-31600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-29100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-69800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-35700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-19300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>311500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>6300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>57800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-19400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>219500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-516400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>120600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-296800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-5400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-31200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-82500</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,31 +9987,32 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>74800</v>
+      </c>
+      <c r="E96" s="3">
         <v>71900</v>
-      </c>
-      <c r="E96" s="3">
-        <v>71400</v>
       </c>
       <c r="F96" s="3">
         <v>71400</v>
       </c>
       <c r="G96" s="3">
+        <v>71400</v>
+      </c>
+      <c r="H96" s="3">
         <v>71000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>70300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>69500</v>
-      </c>
-      <c r="J96" s="3">
-        <v>69400</v>
       </c>
       <c r="K96" s="3">
         <v>69400</v>
@@ -9794,7 +10027,7 @@
         <v>69400</v>
       </c>
       <c r="O96" s="3">
-        <v>-69300</v>
+        <v>69400</v>
       </c>
       <c r="P96" s="3">
         <v>-69300</v>
@@ -9806,64 +10039,64 @@
         <v>-69300</v>
       </c>
       <c r="S96" s="3">
+        <v>-69300</v>
+      </c>
+      <c r="T96" s="3">
         <v>-68600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-66300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-64800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-63200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-62600</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-61700</v>
       </c>
       <c r="Y96" s="3">
         <v>-61700</v>
       </c>
       <c r="Z96" s="3">
+        <v>-61700</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-92400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-88200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-85500</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-81500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-80300</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-80200</v>
       </c>
       <c r="AF96" s="3">
         <v>-80200</v>
       </c>
       <c r="AG96" s="3">
+        <v>-80200</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-81900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-82800</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-95300</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-26100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-30700</v>
-      </c>
-      <c r="AL96" s="3">
-        <v>-30000</v>
       </c>
       <c r="AM96" s="3">
         <v>-30000</v>
@@ -9871,8 +10104,11 @@
       <c r="AN96" s="3">
         <v>-30000</v>
       </c>
+      <c r="AO96" s="3">
+        <v>-30000</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10223,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10342,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,352 +10461,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100900</v>
+      </c>
+      <c r="E100" s="3">
         <v>206200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>36700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-101200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-101000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-14000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-46400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-20200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-136400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-68500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-196100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-13500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-91600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>56000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-112500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-274600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>371600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-69300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-60100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-60400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-90500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>8900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-50400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-83500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-424800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-87500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-212800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-138400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-161800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-114400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>341000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>317900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-16700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-43300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-5000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-300</v>
       </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>-600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>600</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>600</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-100</v>
-      </c>
-      <c r="U101" s="3">
-        <v>100</v>
       </c>
       <c r="V101" s="3">
         <v>100</v>
       </c>
       <c r="W101" s="3">
+        <v>100</v>
+      </c>
+      <c r="X101" s="3">
         <v>300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-200</v>
       </c>
-      <c r="AI101" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
         <v>600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>100</v>
       </c>
-      <c r="AL101" s="3">
-        <v>0</v>
-      </c>
       <c r="AM101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="3">
         <v>-700</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-129400</v>
+      </c>
+      <c r="E102" s="3">
         <v>105900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>72800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-37400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>26700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-23600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>19200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-15200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>22800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-40400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>42200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-86600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-435500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>477500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>44400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-36000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>23700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-25600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>13300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>9500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-17800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>24800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-27000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-79900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-86100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>167500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-529300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>544100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>20700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-12700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>6000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-84200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/SBRA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SBRA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
   <si>
     <t>SBRA</t>
   </si>
@@ -656,530 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>223700</v>
+      </c>
+      <c r="E8" s="3">
         <v>210800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>191300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>190000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>183800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>182100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>178200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>176200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>166200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>162600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>161000</v>
-      </c>
-      <c r="N8" s="3">
-        <v>160500</v>
       </c>
       <c r="O8" s="3">
         <v>160500</v>
       </c>
       <c r="P8" s="3">
+        <v>160500</v>
+      </c>
+      <c r="Q8" s="3">
         <v>165000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>140800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>156000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>163100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>135700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>128600</v>
-      </c>
-      <c r="V8" s="3">
-        <v>152400</v>
       </c>
       <c r="W8" s="3">
         <v>152400</v>
       </c>
       <c r="X8" s="3">
+        <v>152400</v>
+      </c>
+      <c r="Y8" s="3">
         <v>151500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>142100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>153900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>149300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>155800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>149800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>152500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>136800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>139200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>151800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>166300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>166100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>166500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>111800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>64700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>62700</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>61800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>61900</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>85400</v>
+      </c>
+      <c r="E9" s="3">
         <v>80000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>69400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>60900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>59800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>59200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>58500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>54700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>53900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>49500</v>
-      </c>
-      <c r="M9" s="3">
-        <v>49200</v>
       </c>
       <c r="N9" s="3">
         <v>49200</v>
       </c>
       <c r="O9" s="3">
+        <v>49200</v>
+      </c>
+      <c r="P9" s="3">
         <v>47600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>39200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>36700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>34000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>33100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>30900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>30000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>28500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>28000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>26900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>26500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>26300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>27000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>26000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>24000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>24200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>12000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>12500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>12600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>12300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>12100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>5900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>5100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>4400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2400</v>
-      </c>
-      <c r="AN9" s="3">
-        <v>1400</v>
       </c>
       <c r="AO9" s="3">
         <v>1400</v>
       </c>
+      <c r="AP9" s="3">
+        <v>1400</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>138200</v>
+      </c>
+      <c r="E10" s="3">
         <v>130700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>121800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>129100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>124000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>122800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>119800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>121500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>112300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>113100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>111800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>111300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>112900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>125800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>104100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>122000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>130000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>104800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>98600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>123900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>124400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>124600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>115600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>127600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>122300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>129800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>125800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>128300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>124800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>126700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>139200</v>
-      </c>
-      <c r="AH10" s="3">
-        <v>154000</v>
       </c>
       <c r="AI10" s="3">
         <v>154000</v>
       </c>
       <c r="AJ10" s="3">
+        <v>154000</v>
+      </c>
+      <c r="AK10" s="3">
         <v>160600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>106700</v>
-      </c>
-      <c r="AL10" s="3">
-        <v>60300</v>
       </c>
       <c r="AM10" s="3">
         <v>60300</v>
       </c>
       <c r="AN10" s="3">
+        <v>60300</v>
+      </c>
+      <c r="AO10" s="3">
         <v>60400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>60500</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1221,8 +1234,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1340,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,116 +1476,119 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>400</v>
+      </c>
+      <c r="E14" s="3">
         <v>6900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-6900</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>-7100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>13500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>8000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>42300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>7800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>29800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>21200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>61000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>11700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-2000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>43400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2200</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>1700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>6000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>2100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>8300</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>14600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-45100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>103100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>2900</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>500</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>1300</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>600</v>
       </c>
-      <c r="AL14" s="3">
-        <v>0</v>
-      </c>
       <c r="AM14" s="3">
         <v>0</v>
       </c>
@@ -1578,73 +1598,76 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>53100</v>
+      </c>
+      <c r="E15" s="3">
         <v>51400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>48500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>43600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>43500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>42300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>42700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>41700</v>
-      </c>
-      <c r="K15" s="3">
-        <v>42900</v>
       </c>
       <c r="L15" s="3">
         <v>42900</v>
       </c>
       <c r="M15" s="3">
+        <v>42900</v>
+      </c>
+      <c r="N15" s="3">
         <v>43200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>44100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>52800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>49900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>47400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>45200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>45300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>45100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>45000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>44500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>44400</v>
-      </c>
-      <c r="X15" s="3">
-        <v>44200</v>
       </c>
       <c r="Y15" s="3">
         <v>44200</v>
@@ -1656,49 +1679,52 @@
         <v>44200</v>
       </c>
       <c r="AB15" s="3">
+        <v>44200</v>
+      </c>
+      <c r="AC15" s="3">
         <v>44000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>43100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>49500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>44900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>48100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>48500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>46800</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>48000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>51600</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>25900</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>17200</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>19100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>17200</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,246 +1763,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>153400</v>
+      </c>
+      <c r="E17" s="3">
         <v>160800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>131900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>117000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>116000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>114500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>113600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>109100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>108700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>109100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>103200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>102800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>110900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>153900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>186800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>129700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>117200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>160300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>115200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>110900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>114700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>111800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>114000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>112000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>111500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>116500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>125300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>67000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>211100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>141700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>115500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>105500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>105900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>109500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>97500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>49000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>45800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>40800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>70200</v>
+      </c>
+      <c r="E18" s="3">
         <v>50000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>59400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>73000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>67800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>67600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>64600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>67100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>57500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>53600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>57800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>57700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>49600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-46000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>26300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>45900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-24600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>41500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>37700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>39700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>28100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>41900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>37800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>39300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>24500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>85500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-74300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>36300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>60800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>60200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>57000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>14300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>15700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>16900</v>
-      </c>
-      <c r="AN18" s="3">
-        <v>21000</v>
       </c>
       <c r="AO18" s="3">
         <v>21000</v>
       </c>
+      <c r="AP18" s="3">
+        <v>21000</v>
+      </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,288 +2051,295 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>3700</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3">
         <v>-13700</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>-100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>2000</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-96000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-9200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-173500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>8200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-11900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-15700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>140600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>47400</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>5000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>2100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>2400</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>123300</v>
+      </c>
+      <c r="E21" s="3">
         <v>97700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>107900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>130300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>111300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>109900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>107400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>108900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>100300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>96500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>99100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>101800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>102400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-34900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-2100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>62200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>86100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>21300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>55400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-87600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>78500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>80600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>80500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>74300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>80400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>84900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>67200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>134000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-32100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>29900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>84400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>248200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>111000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>155400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>41400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>37900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>38100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>40600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>42600</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>28400</v>
+      </c>
+      <c r="E22" s="3">
         <v>11700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>28900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>27500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>27100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>27600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>29500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>29300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>28400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>27900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>28200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>28300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>28500</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -2375,127 +2415,133 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E23" s="3">
         <v>27600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>23000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>66000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>40700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>47100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>29500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>24400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>26700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>17600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-14600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>21500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-8800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-84800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-49500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>17100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>40900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-23800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>10300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-132100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>34100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>36500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>36300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>30100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>36300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>40900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>24100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>84500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-77100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-18200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>36000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>201400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>63000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>104500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>14900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>20700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>19000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>23400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>25500</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2503,25 +2549,25 @@
         <v>500</v>
       </c>
       <c r="E24" s="3">
+        <v>500</v>
+      </c>
+      <c r="F24" s="3">
         <v>400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>500</v>
-      </c>
-      <c r="G24" s="3">
-        <v>400</v>
       </c>
       <c r="H24" s="3">
         <v>400</v>
       </c>
       <c r="I24" s="3">
+        <v>400</v>
+      </c>
+      <c r="J24" s="3">
         <v>-300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>400</v>
-      </c>
-      <c r="K24" s="3">
-        <v>500</v>
       </c>
       <c r="L24" s="3">
         <v>500</v>
@@ -2530,91 +2576,94 @@
         <v>500</v>
       </c>
       <c r="N24" s="3">
+        <v>500</v>
+      </c>
+      <c r="O24" s="3">
         <v>300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>600</v>
-      </c>
-      <c r="R24" s="3">
-        <v>300</v>
       </c>
       <c r="S24" s="3">
         <v>300</v>
       </c>
       <c r="T24" s="3">
+        <v>300</v>
+      </c>
+      <c r="U24" s="3">
         <v>500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>600</v>
-      </c>
-      <c r="AI24" s="3">
-        <v>500</v>
       </c>
       <c r="AJ24" s="3">
         <v>500</v>
       </c>
       <c r="AK24" s="3">
+        <v>500</v>
+      </c>
+      <c r="AL24" s="3">
         <v>-200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,246 +2781,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>40800</v>
+      </c>
+      <c r="E26" s="3">
         <v>27100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>22500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>65500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>40300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>46700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>29800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>24000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>26300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>17200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-15100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>21200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-84900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-50100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>16800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>40600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-24400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>10200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-132600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>33400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>37100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>36500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>29600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>35200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>39700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>23300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>83700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-77700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-19400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>35200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>200800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>62500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>104000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>15100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>20500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>18800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>23200</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>25300</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E27" s="3">
         <v>27200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>22500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>65500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>40300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>46700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>29800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>24000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>26300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>17200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-15100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>21200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-84900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-50100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>16800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>40600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-24400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>10200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-132600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>33400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>37100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>36500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>29600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>35200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>39700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>23300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>83700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-77700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-19400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>35200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>193600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>59900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>101400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>12500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>18000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>16300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>20600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3208,8 +3269,11 @@
       <c r="AO29" s="3">
         <v>0</v>
       </c>
+      <c r="AP29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,246 +3513,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3700</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3">
         <v>13700</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-2000</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3">
         <v>96000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>9200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>173500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>11900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>15700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-140600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-47400</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-5000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-4400</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E33" s="3">
         <v>27200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>22500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>65500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>40300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>46700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>29800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>24000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>26300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>21200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-84900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-50100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>16800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>40600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-24400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>10200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-132600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>33400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>37100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>36500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>29600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>35200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>39700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>23300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>83700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-77700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-19400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>35200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>193600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>59900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>101400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>12500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>18000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>16300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>20600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,251 +3879,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E35" s="3">
         <v>27200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>22500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>65500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>40300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>46700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>29800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>24000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>26300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>21200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-84900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-50100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>16800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>40600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-24400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>10200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-132600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>33400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>37100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>36500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>29600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>35200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>39700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>23300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>83700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-77700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-19400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>35200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>193600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>59900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>101400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>12500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>18000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>16300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>20600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,169 +4218,173 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>116500</v>
+      </c>
+      <c r="E41" s="3">
         <v>71500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>200600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>95200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>22700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>60500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>63000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>36400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>59900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>41300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>33300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>27200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>33500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>49300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>26300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>67200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>24800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>112000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>546300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>69300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>24900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>59100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>35000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>28300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>54100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>39100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>29400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>47600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>22900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>50200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>36300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>38800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>46400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>518600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>30900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>13200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>12800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>25700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>19700</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E42" s="3">
         <v>3400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>3800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>15200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>20400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>10300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>27000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>27100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>18900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>39300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>31100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>19800</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4370,50 +4460,53 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>132200</v>
+      </c>
+      <c r="E43" s="3">
         <v>134600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>139600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>42300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>46600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>150200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>46400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>46100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>43700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>147100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>42000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>42300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>37400</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -4489,8 +4582,11 @@
       <c r="AO43" s="3">
         <v>0</v>
       </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4530,8 +4626,8 @@
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4608,13 +4704,16 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>33200</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>8</v>
@@ -4649,8 +4748,8 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
+      <c r="P45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q45" s="3">
         <v>0</v>
@@ -4709,68 +4808,71 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>8</v>
+      <c r="AJ45" s="3">
+        <v>0</v>
       </c>
       <c r="AK45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AL45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM45" s="3">
         <v>141200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>126000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>125300</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>116400</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>296600</v>
+      </c>
+      <c r="E46" s="3">
         <v>216100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>350900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>149000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>90800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>237000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>125700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>115400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>136700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>212700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>120200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>105800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>95900</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4846,354 +4948,363 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>182400</v>
+      </c>
+      <c r="E47" s="3">
         <v>183500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>182000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>189500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>182800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>182900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>190600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>187100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>191800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>194700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>192700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>196100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>192100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>546400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>597900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>615300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>491000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>495800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>215800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>219200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>385000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>391600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>397600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>379700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>400100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>426800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>432600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>439400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>444900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>453800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>454700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>456200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>455800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>114400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>149800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>94200</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>96500</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>96000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>94500</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4709200</v>
+      </c>
+      <c r="E48" s="3">
         <v>4692900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4636400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4486100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4495000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4520700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4581500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4576900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4588700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4628900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4603000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4751900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4797000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4959300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5018900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5045100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5156100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5162900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5228700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5269400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5279400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5285000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5306300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5358500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5363200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5350700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5354400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5388400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>5447200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5853500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5975600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5993700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>6108800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>5994400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>5972800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1995900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1993600</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2009900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1999800</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>67400</v>
+      </c>
+      <c r="E49" s="3">
         <v>65300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>59800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>24700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>24800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>27500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>28800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>27700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>28300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>30900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>32700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>36000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>39400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>40100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>48300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>49800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>52900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>54100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>76400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>79700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>81500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>82800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>85900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>93500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>96800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>101500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>105000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>108900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>119700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>131100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>142900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>156300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>161400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>167100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>262800</v>
       </c>
-      <c r="AL49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM49" s="3" t="s">
         <v>8</v>
       </c>
@@ -5203,8 +5314,11 @@
       <c r="AO49" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP49" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,8 +5558,11 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5452,116 +5572,119 @@
       <c r="E52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
         <v>143200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>104200</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3">
         <v>103900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>108500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>109900</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="3">
         <v>112900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>115500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>112900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4900</v>
-      </c>
-      <c r="R52" s="3">
-        <v>4400</v>
       </c>
       <c r="S52" s="3">
         <v>4400</v>
       </c>
       <c r="T52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="U52" s="3">
         <v>3900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5100</v>
-      </c>
-      <c r="V52" s="3">
-        <v>4600</v>
       </c>
       <c r="W52" s="3">
         <v>4600</v>
       </c>
       <c r="X52" s="3">
+        <v>4600</v>
+      </c>
+      <c r="Y52" s="3">
         <v>6400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>8600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>8400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>9900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>280500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>103200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>186800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>11800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>68800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>12500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>9400</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>11200</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>9000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>5591200</v>
+      </c>
+      <c r="E54" s="3">
         <v>5493400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5564800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5328000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5233200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5303700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5366100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5351100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5374400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5386200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5380600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5524300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5556300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5747700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5844900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5961400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5884900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5966700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6209500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5822100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5963800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5985600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5991600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>6023600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>6092300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>6069300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>6068000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>6123200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>6455100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>6665300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>6910300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>7028100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>6984600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>7032300</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>6588300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>2254000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>2240100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>2265900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>2239400</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,169 +6014,173 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E57" s="3">
         <v>73200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>71900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>65600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>61800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>67800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>71300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>62500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>59000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>73800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>78300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>74700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>94000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>124100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>123200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>101100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>92900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>121500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>108600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>103300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>105900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>130200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>125600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>143300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>112500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>98400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>92100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>90800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>72900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>94800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>86900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>105300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>102400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>102500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>116100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>37100</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>33400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>39600</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E58" s="3">
         <v>4500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2700</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>1100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2500</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1500</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -6122,85 +6256,88 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E59" s="3">
         <v>32500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>21000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>22100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>25700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>19500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>20800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>20000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>34200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>28600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>30800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>27600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>22000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>25400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>21500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>18200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>16100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>17600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>16100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>18100</v>
       </c>
-      <c r="Z59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB59" s="3">
-        <v>9800</v>
+      <c r="AB59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC59" s="3">
         <v>9800</v>
@@ -6209,16 +6346,16 @@
         <v>9800</v>
       </c>
       <c r="AE59" s="3">
+        <v>9800</v>
+      </c>
+      <c r="AF59" s="3">
         <v>10000</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AG59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH59" s="3">
-        <v>0</v>
+      <c r="AH59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI59" s="3">
         <v>0</v>
@@ -6241,50 +6378,53 @@
       <c r="AO59" s="3">
         <v>0</v>
       </c>
+      <c r="AP59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>113100</v>
+      </c>
+      <c r="E60" s="3">
         <v>119700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>117300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>107000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>106700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>109600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>115200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>102200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>102900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>124500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>128500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>122900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>144500</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6360,169 +6500,175 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2670000</v>
+      </c>
+      <c r="E61" s="3">
         <v>2533100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2597900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2485700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2399200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2425900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2477800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2457300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2473300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2426600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2349000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2419000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2395100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2506800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2446900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2480200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2357500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2394500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2702100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2266300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2281600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2372400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2423000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2455300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2479300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2402100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2603100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2686000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3230200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>3232000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>3368600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>3423800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>3361100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>3394500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>3005500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1220100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1202400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1210700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1187400</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E62" s="3">
         <v>16800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>22600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>25000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>26800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>28300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>29700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>31100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>32500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>34200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>38700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>40500</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
       <c r="Q62" s="3">
         <v>0</v>
       </c>
@@ -6598,8 +6744,11 @@
       <c r="AO62" s="3">
         <v>0</v>
       </c>
+      <c r="AP62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2803300</v>
+      </c>
+      <c r="E66" s="3">
         <v>2669600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2737800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2616500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2531000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2562400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2621300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2589100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2607300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2583600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2511700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2580600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2580100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2691300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2636200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2643700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2523400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2587200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2880400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2439100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2460400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2576400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2627300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2662300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2697100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2580800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2785600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2867100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3408700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3414900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3547400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3624600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3562400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3599500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>3219200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1257300</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1235800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1250300</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1225600</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7454,7 +7622,7 @@
         <v>0</v>
       </c>
       <c r="AI70" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AJ70" s="3">
         <v>100</v>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>100</v>
       </c>
+      <c r="AP70" s="3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,8 +7764,11 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7634,86 +7808,89 @@
       <c r="O72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-1451900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-1296900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-1177000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-1124100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1095200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-1001200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-944500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-746500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-716200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-689800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-663900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-631300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-573300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-523700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-460800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-462600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-271600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-171100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-125600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-238600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-217200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-225500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-214100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-203600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-192200</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-185000</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2786000</v>
+      </c>
+      <c r="E76" s="3">
         <v>2821800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2824900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2711500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2702200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2741300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2744800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2762000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2767200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2802500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2868900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2943700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2976200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3056400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3208700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3317700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3361500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3379500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3329100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3383100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3503400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3409200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3364300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3361300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3395200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3488500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3282400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3256100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3046500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3250400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3362900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3403500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3422100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3432700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3369000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>996600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1004300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1015500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>1013800</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,251 +8496,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E81" s="3">
         <v>27200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>22500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>65500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>40300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>46700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>29800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>24000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>26300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>21200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-84900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-50100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>16800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>40600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-24400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>10200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-132600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>33400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>37100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>36500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>29600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>35200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>39700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>23300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>83700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-77700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-19400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>35200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>193600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>59900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>101400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>12500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>18000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>16300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>20600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,73 +8791,74 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E83" s="3">
         <v>34800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>42700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>41700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>42900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>31300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>43200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>44100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>52800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>32300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>47400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>45200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>45300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>49900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>47400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>45200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>45300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>45100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>45000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>44500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>44400</v>
-      </c>
-      <c r="X83" s="3">
-        <v>44200</v>
       </c>
       <c r="Y83" s="3">
         <v>44200</v>
@@ -8671,49 +8870,52 @@
         <v>44200</v>
       </c>
       <c r="AB83" s="3">
+        <v>44200</v>
+      </c>
+      <c r="AC83" s="3">
         <v>44000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>43100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>49500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>44900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>48100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>48500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>46800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>48000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>51000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>26600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>17200</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>19100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>17200</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>17100</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>98400</v>
+      </c>
+      <c r="E89" s="3">
         <v>87400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>100000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>81000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>80300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>80000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>97700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>80100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>52800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>78700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>83200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>70300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>68300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>67600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>108500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>76600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>63100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>97900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>106200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>83700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>68500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>89400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>96900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>93800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>74800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>95500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>85100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>137900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>54000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>77600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>71500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>109900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>101600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>82500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-1000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>22700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>31600</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>42900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>39300</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,8 +9689,9 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9510,86 +9731,89 @@
       <c r="O91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P91" s="3">
+      <c r="P91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-63400</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-20600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-37300</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-33500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-28700</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
-      </c>
       <c r="Y91" s="3">
         <v>0</v>
       </c>
       <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-25700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-67300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-36200</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AE91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-22500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-25000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-11500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-3700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,127 +10053,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-105100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-116500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-199800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-45100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>18600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-57000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-57300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-61800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>59900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>113200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-31200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-57000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-90900</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-37200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-258800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-41900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-35400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-31600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-29100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-69800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-35700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-19300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>311500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>6300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>57800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-19400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>219500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-516400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>120600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-296800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-5400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-31200</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-82500</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,34 +10221,35 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>75700</v>
+      </c>
+      <c r="E96" s="3">
         <v>74800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>71900</v>
-      </c>
-      <c r="F96" s="3">
-        <v>71400</v>
       </c>
       <c r="G96" s="3">
         <v>71400</v>
       </c>
       <c r="H96" s="3">
+        <v>71400</v>
+      </c>
+      <c r="I96" s="3">
         <v>71000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>70300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>69500</v>
-      </c>
-      <c r="K96" s="3">
-        <v>69400</v>
       </c>
       <c r="L96" s="3">
         <v>69400</v>
@@ -10030,7 +10264,7 @@
         <v>69400</v>
       </c>
       <c r="P96" s="3">
-        <v>-69300</v>
+        <v>69400</v>
       </c>
       <c r="Q96" s="3">
         <v>-69300</v>
@@ -10042,64 +10276,64 @@
         <v>-69300</v>
       </c>
       <c r="T96" s="3">
+        <v>-69300</v>
+      </c>
+      <c r="U96" s="3">
         <v>-68600</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-66300</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-64800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-63200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-62600</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-61700</v>
       </c>
       <c r="Z96" s="3">
         <v>-61700</v>
       </c>
       <c r="AA96" s="3">
+        <v>-61700</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-92400</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-88200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-85500</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-81500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-80300</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-80200</v>
       </c>
       <c r="AG96" s="3">
         <v>-80200</v>
       </c>
       <c r="AH96" s="3">
+        <v>-80200</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-81900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-82800</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-95300</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-26100</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-30700</v>
-      </c>
-      <c r="AM96" s="3">
-        <v>-30000</v>
       </c>
       <c r="AN96" s="3">
         <v>-30000</v>
@@ -10107,8 +10341,11 @@
       <c r="AO96" s="3">
         <v>-30000</v>
       </c>
+      <c r="AP96" s="3">
+        <v>-30000</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,361 +10707,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>206200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>36700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-101200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-101000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-14000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-46400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-20200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-9400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-136400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-68500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-196100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-91600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>56000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-112500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-274600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>371600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-69300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-60100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-60400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-90500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>8900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-50400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-83500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-424800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-87500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-212800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-138400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-161800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-114400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>341000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>317900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-16700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-43300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-5000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-41700</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>600</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>-100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>600</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
         <v>0</v>
       </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-100</v>
-      </c>
-      <c r="V101" s="3">
-        <v>100</v>
       </c>
       <c r="W101" s="3">
         <v>100</v>
       </c>
       <c r="X101" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y101" s="3">
         <v>300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
       <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
         <v>600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>100</v>
       </c>
-      <c r="AM101" s="3">
-        <v>0</v>
-      </c>
       <c r="AN101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO101" s="3">
         <v>-700</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-129400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>105900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>72800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-37400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>26700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-23600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>19200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>7900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-15200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>22800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-40400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>42200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-86600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-435500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>477500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>44400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-36000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>23700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-25600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>13300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>9500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-17800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>24800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-27000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-79900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-86100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>167500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-529300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>544100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>20700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-12700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>6000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-84200</v>
       </c>
     </row>
